--- a/Bao_Cao_Khao_Sat_Dau_Nam_va_76_HS_CKDV_2026.xlsx
+++ b/Bao_Cao_Khao_Sat_Dau_Nam_va_76_HS_CKDV_2026.xlsx
@@ -7177,13 +7177,13 @@
         <v>CS2</v>
       </c>
       <c r="C5" t="str">
-        <v>HS065</v>
+        <v>0601021777</v>
       </c>
       <c r="D5" t="str">
         <v>Lê Gia Lân</v>
       </c>
       <c r="E5" t="str">
-        <v>Chưa rõ</v>
+        <v>1.3_CS2</v>
       </c>
       <c r="F5" t="str">
         <v>Khối 1</v>
@@ -7212,13 +7212,13 @@
         <v>CS2</v>
       </c>
       <c r="C6" t="str">
-        <v>HS079</v>
+        <v>0601021457</v>
       </c>
       <c r="D6" t="str">
         <v>Đào Trần Thảo Linh</v>
       </c>
       <c r="E6" t="str">
-        <v>Chưa rõ</v>
+        <v>1.3_CS2</v>
       </c>
       <c r="F6" t="str">
         <v>Khối 1</v>
@@ -7247,7 +7247,7 @@
         <v>CS1</v>
       </c>
       <c r="C7" t="str">
-        <v>HS105</v>
+        <v>0601011426</v>
       </c>
       <c r="D7" t="str">
         <v>Lê Nguyên Khang</v>
@@ -7282,7 +7282,7 @@
         <v>CS3</v>
       </c>
       <c r="C8" t="str">
-        <v>HS148</v>
+        <v>0701030370</v>
       </c>
       <c r="D8" t="str">
         <v>Phan Anh Quân</v>
@@ -7317,7 +7317,7 @@
         <v>CS3</v>
       </c>
       <c r="C9" t="str">
-        <v>HS163</v>
+        <v>0701030387</v>
       </c>
       <c r="D9" t="str">
         <v>Đoàn Ngọc Thảo Chloe</v>
@@ -7352,7 +7352,7 @@
         <v>CS1</v>
       </c>
       <c r="C10" t="str">
-        <v>HS249</v>
+        <v>0601011201</v>
       </c>
       <c r="D10" t="str">
         <v>Mai Huy Thắng</v>
@@ -7387,7 +7387,7 @@
         <v>CS1</v>
       </c>
       <c r="C11" t="str">
-        <v>HS288</v>
+        <v>0601012396</v>
       </c>
       <c r="D11" t="str">
         <v xml:space="preserve">Trần Hoàng Anh </v>
@@ -7422,7 +7422,7 @@
         <v>CS1</v>
       </c>
       <c r="C12" t="str">
-        <v>HS307</v>
+        <v>0601012393</v>
       </c>
       <c r="D12" t="str">
         <v>Nguyễn Thanh Thảo</v>
@@ -7457,7 +7457,7 @@
         <v>CS1</v>
       </c>
       <c r="C13" t="str">
-        <v>HS308</v>
+        <v>0601011617</v>
       </c>
       <c r="D13" t="str">
         <v>Lê Khánh Hà</v>
@@ -7492,7 +7492,7 @@
         <v>CS1</v>
       </c>
       <c r="C14" t="str">
-        <v>HS701020014</v>
+        <v>0601012399</v>
       </c>
       <c r="D14" t="str">
         <v>Ngô Thục Đan</v>
@@ -7527,13 +7527,13 @@
         <v>CS2</v>
       </c>
       <c r="C15" t="str">
-        <v>HS701020036</v>
+        <v>0601021828</v>
       </c>
       <c r="D15" t="str">
         <v>Phan Hải Đăng</v>
       </c>
       <c r="E15" t="str">
-        <v>Chưa rõ</v>
+        <v>1.3_CS2</v>
       </c>
       <c r="F15" t="str">
         <v>Khối 1</v>
@@ -7562,13 +7562,13 @@
         <v>CS3</v>
       </c>
       <c r="C16" t="str">
-        <v>HS701020076</v>
+        <v>0701030397</v>
       </c>
       <c r="D16" t="str">
         <v>Govorushko Mikhail</v>
       </c>
       <c r="E16" t="str">
-        <v>Chưa rõ</v>
+        <v>1.1INT_CS3</v>
       </c>
       <c r="F16" t="str">
         <v>Khối 1</v>
@@ -7597,7 +7597,7 @@
         <v>CS3</v>
       </c>
       <c r="C17" t="str">
-        <v>HS701020085</v>
+        <v>0701030402</v>
       </c>
       <c r="D17" t="str">
         <v>Lecomte Mailys Mộc Yên</v>
@@ -7632,7 +7632,7 @@
         <v>CS4</v>
       </c>
       <c r="C18" t="str">
-        <v>HS202</v>
+        <v>0602040621</v>
       </c>
       <c r="D18" t="str">
         <v>Võ Thị Anh Thư</v>
@@ -7667,13 +7667,13 @@
         <v>CS2</v>
       </c>
       <c r="C19" t="str">
-        <v>HS701020105</v>
+        <v>0601021795</v>
       </c>
       <c r="D19" t="str">
         <v>Lê Hồ Duy Khang</v>
       </c>
       <c r="E19" t="str">
-        <v>Chưa rõ</v>
+        <v>1.3_CS2</v>
       </c>
       <c r="F19" t="str">
         <v>Khối 1</v>
@@ -7702,13 +7702,13 @@
         <v>CS1</v>
       </c>
       <c r="C20" t="str">
-        <v>HS701020134</v>
+        <v>0601012303</v>
       </c>
       <c r="D20" t="str">
         <v>Nguyễn Daniil</v>
       </c>
       <c r="E20" t="str">
-        <v>Chưa rõ</v>
+        <v>1.1_CS1</v>
       </c>
       <c r="F20" t="str">
         <v>Khối 1</v>
@@ -7737,7 +7737,7 @@
         <v>CS1</v>
       </c>
       <c r="C21" t="str">
-        <v>HS701020183</v>
+        <v>0601012153</v>
       </c>
       <c r="D21" t="str">
         <v>Nguyễn Ngọc Minh</v>
@@ -7772,13 +7772,13 @@
         <v>CS2</v>
       </c>
       <c r="C22" t="str">
-        <v>HS701020188</v>
+        <v>0701020109</v>
       </c>
       <c r="D22" t="str">
         <v>Sangadziev Aron</v>
       </c>
       <c r="E22" t="str">
-        <v>Chưa rõ</v>
+        <v>1.2INT_CS2</v>
       </c>
       <c r="F22" t="str">
         <v>Khối 1</v>
@@ -7868,7 +7868,7 @@
         <v>CS1</v>
       </c>
       <c r="C6" t="str">
-        <v>HS101</v>
+        <v>0701030312</v>
       </c>
       <c r="D6" t="str">
         <v>Nguyễn Gia Bảo</v>
@@ -7903,7 +7903,7 @@
         <v>CS1</v>
       </c>
       <c r="C7" t="str">
-        <v>HS105</v>
+        <v>0601011426</v>
       </c>
       <c r="D7" t="str">
         <v>Lê Nguyên Khang</v>
@@ -7938,7 +7938,7 @@
         <v>CS1</v>
       </c>
       <c r="C8" t="str">
-        <v>HS111</v>
+        <v>0601012314</v>
       </c>
       <c r="D8" t="str">
         <v>Phạm Nguyễn Minh Anh</v>
@@ -7973,7 +7973,7 @@
         <v>CS1</v>
       </c>
       <c r="C9" t="str">
-        <v>HS246</v>
+        <v>0601012372</v>
       </c>
       <c r="D9" t="str">
         <v>Phan Đình Phùng</v>
@@ -8008,7 +8008,7 @@
         <v>CS1</v>
       </c>
       <c r="C10" t="str">
-        <v>HS249</v>
+        <v>0601011201</v>
       </c>
       <c r="D10" t="str">
         <v>Mai Huy Thắng</v>
@@ -8043,7 +8043,7 @@
         <v>CS1</v>
       </c>
       <c r="C11" t="str">
-        <v>HS252</v>
+        <v>0601012363</v>
       </c>
       <c r="D11" t="str">
         <v xml:space="preserve">Phạm Thùy Gia Hân </v>
@@ -8078,7 +8078,7 @@
         <v>CS1</v>
       </c>
       <c r="C12" t="str">
-        <v>HS256</v>
+        <v>0601012381</v>
       </c>
       <c r="D12" t="str">
         <v>Nguyễn Bình Phương An</v>
@@ -8113,7 +8113,7 @@
         <v>CS1</v>
       </c>
       <c r="C13" t="str">
-        <v>HS257</v>
+        <v>0601050347</v>
       </c>
       <c r="D13" t="str">
         <v>Lê Bảo Trâm</v>
@@ -8148,7 +8148,7 @@
         <v>CS1</v>
       </c>
       <c r="C14" t="str">
-        <v>HS258</v>
+        <v>0601011593</v>
       </c>
       <c r="D14" t="str">
         <v>Lê Bảo Châu</v>
@@ -8183,7 +8183,7 @@
         <v>CS1</v>
       </c>
       <c r="C15" t="str">
-        <v>HS259</v>
+        <v>0601012376</v>
       </c>
       <c r="D15" t="str">
         <v>Phạm Gia Hương</v>
@@ -8218,13 +8218,13 @@
         <v>CS1</v>
       </c>
       <c r="C16" t="str">
-        <v>HS265</v>
+        <v>0601012390</v>
       </c>
       <c r="D16" t="str">
         <v xml:space="preserve">Đỗ An Nhiên </v>
       </c>
       <c r="E16" t="str">
-        <v>Chưa rõ</v>
+        <v>1.1_CS1</v>
       </c>
       <c r="F16" t="str">
         <v>Khối 1</v>
@@ -8253,13 +8253,13 @@
         <v>CS1</v>
       </c>
       <c r="C17" t="str">
-        <v>HS275</v>
+        <v>0602040631</v>
       </c>
       <c r="D17" t="str">
         <v>Hà Đặng Phước Huy</v>
       </c>
       <c r="E17" t="str">
-        <v>Chưa rõ</v>
+        <v>1S_CS4</v>
       </c>
       <c r="F17" t="str">
         <v>Khối 1</v>
@@ -8288,7 +8288,7 @@
         <v>CS1</v>
       </c>
       <c r="C18" t="str">
-        <v>HS288</v>
+        <v>0601012396</v>
       </c>
       <c r="D18" t="str">
         <v xml:space="preserve">Trần Hoàng Anh </v>
@@ -8323,7 +8323,7 @@
         <v>CS1</v>
       </c>
       <c r="C19" t="str">
-        <v>HS306</v>
+        <v>0701010055</v>
       </c>
       <c r="D19" t="str">
         <v>Nguyễn Ngọc Thiên Bảo</v>
@@ -8358,7 +8358,7 @@
         <v>CS1</v>
       </c>
       <c r="C20" t="str">
-        <v>HS307</v>
+        <v>0601012393</v>
       </c>
       <c r="D20" t="str">
         <v>Nguyễn Thanh Thảo</v>
@@ -8393,7 +8393,7 @@
         <v>CS1</v>
       </c>
       <c r="C21" t="str">
-        <v>HS308</v>
+        <v>0601011617</v>
       </c>
       <c r="D21" t="str">
         <v>Lê Khánh Hà</v>
@@ -8428,7 +8428,7 @@
         <v>CS1</v>
       </c>
       <c r="C22" t="str">
-        <v>HS311</v>
+        <v>0601012394</v>
       </c>
       <c r="D22" t="str">
         <v xml:space="preserve">Nguyễn Đại Phúc </v>
@@ -8469,7 +8469,7 @@
         <v>LÊ ĐÌNH SĨ PHÚ</v>
       </c>
       <c r="E23" t="str">
-        <v>Chưa rõ</v>
+        <v>6.1_CS1</v>
       </c>
       <c r="F23" t="str">
         <v>Khối 6</v>
@@ -8498,7 +8498,7 @@
         <v>CS1</v>
       </c>
       <c r="C24" t="str">
-        <v>HS701020014</v>
+        <v>0601012399</v>
       </c>
       <c r="D24" t="str">
         <v>Ngô Thục Đan</v>
@@ -8533,7 +8533,7 @@
         <v>CS1</v>
       </c>
       <c r="C25" t="str">
-        <v>HS116</v>
+        <v>0601012317</v>
       </c>
       <c r="D25" t="str">
         <v>Lê Nguyệt Cát</v>
@@ -8568,7 +8568,7 @@
         <v>CS1</v>
       </c>
       <c r="C26" t="str">
-        <v>HS129</v>
+        <v>0601012338</v>
       </c>
       <c r="D26" t="str">
         <v>Hoàng Bảo Quyên</v>
@@ -8603,7 +8603,7 @@
         <v>CS1</v>
       </c>
       <c r="C27" t="str">
-        <v>HS131</v>
+        <v>0601012280</v>
       </c>
       <c r="D27" t="str">
         <v>Phạm Gia Bảo</v>
@@ -8638,7 +8638,7 @@
         <v>CS1</v>
       </c>
       <c r="C28" t="str">
-        <v>HS124</v>
+        <v>0601012318</v>
       </c>
       <c r="D28" t="str">
         <v>Đặng Hoàng Như Ý</v>
@@ -8673,7 +8673,7 @@
         <v>CS1</v>
       </c>
       <c r="C29" t="str">
-        <v>HS126</v>
+        <v>0601012334</v>
       </c>
       <c r="D29" t="str">
         <v>Phạm Hải Như</v>
@@ -8708,7 +8708,7 @@
         <v>CS1</v>
       </c>
       <c r="C30" t="str">
-        <v>HS701020117</v>
+        <v>0701030403</v>
       </c>
       <c r="D30" t="str">
         <v>Nguyễn Thành Long</v>
@@ -8743,7 +8743,7 @@
         <v>CS1</v>
       </c>
       <c r="C31" t="str">
-        <v>HS701020124</v>
+        <v>0601012369</v>
       </c>
       <c r="D31" t="str">
         <v>Trần Quang Thiên Ân</v>
@@ -8778,7 +8778,7 @@
         <v>CS1</v>
       </c>
       <c r="C32" t="str">
-        <v>HS701020125</v>
+        <v>0601012312</v>
       </c>
       <c r="D32" t="str">
         <v>Lê Hồ Gia Huy</v>
@@ -8813,7 +8813,7 @@
         <v>CS1</v>
       </c>
       <c r="C33" t="str">
-        <v>HS701020126</v>
+        <v>0601012400</v>
       </c>
       <c r="D33" t="str">
         <v>Trương Lê Hưng Phát</v>
@@ -8848,7 +8848,7 @@
         <v>CS1</v>
       </c>
       <c r="C34" t="str">
-        <v>HS701020122</v>
+        <v>0601012351</v>
       </c>
       <c r="D34" t="str">
         <v>Nguyễn Văn Tuấn Kiệt</v>
@@ -8883,13 +8883,13 @@
         <v>CS1</v>
       </c>
       <c r="C35" t="str">
-        <v>HS701020134</v>
+        <v>0601012303</v>
       </c>
       <c r="D35" t="str">
         <v>Nguyễn Daniil</v>
       </c>
       <c r="E35" t="str">
-        <v>Chưa rõ</v>
+        <v>1.1_CS1</v>
       </c>
       <c r="F35" t="str">
         <v>Khối 1</v>
@@ -8918,7 +8918,7 @@
         <v>CS1</v>
       </c>
       <c r="C36" t="str">
-        <v>HS701020137</v>
+        <v>0601012340</v>
       </c>
       <c r="D36" t="str">
         <v>Trần Đăng Quang</v>
@@ -8953,7 +8953,7 @@
         <v>CS1</v>
       </c>
       <c r="C37" t="str">
-        <v>HS701020139</v>
+        <v>0601012347</v>
       </c>
       <c r="D37" t="str">
         <v>Trần Thục Quyên</v>
@@ -8988,7 +8988,7 @@
         <v>CS1</v>
       </c>
       <c r="C38" t="str">
-        <v>HS701020140</v>
+        <v>0601012348</v>
       </c>
       <c r="D38" t="str">
         <v>Lương Bích Ngọc</v>
@@ -9023,7 +9023,7 @@
         <v>CS1</v>
       </c>
       <c r="C39" t="str">
-        <v>HS701020141</v>
+        <v>0601011972</v>
       </c>
       <c r="D39" t="str">
         <v>Nguyễn Quỳnh Như</v>
@@ -9058,7 +9058,7 @@
         <v>CS1</v>
       </c>
       <c r="C40" t="str">
-        <v>HS701020183</v>
+        <v>0601012153</v>
       </c>
       <c r="D40" t="str">
         <v>Nguyễn Ngọc Minh</v>
@@ -9093,7 +9093,7 @@
         <v>CS1</v>
       </c>
       <c r="C41" t="str">
-        <v>HS701020186</v>
+        <v>0601012421</v>
       </c>
       <c r="D41" t="str">
         <v xml:space="preserve">Nguyễn Đặng Bảo Trâm </v>
@@ -9128,13 +9128,13 @@
         <v>CS2</v>
       </c>
       <c r="C42" t="str">
-        <v>HS065</v>
+        <v>0601021777</v>
       </c>
       <c r="D42" t="str">
         <v>Lê Gia Lân</v>
       </c>
       <c r="E42" t="str">
-        <v>Chưa rõ</v>
+        <v>1.3_CS2</v>
       </c>
       <c r="F42" t="str">
         <v>Khối 1</v>
@@ -9163,13 +9163,13 @@
         <v>CS2</v>
       </c>
       <c r="C43" t="str">
-        <v>HS079</v>
+        <v>0601021457</v>
       </c>
       <c r="D43" t="str">
         <v>Đào Trần Thảo Linh</v>
       </c>
       <c r="E43" t="str">
-        <v>Chưa rõ</v>
+        <v>1.3_CS2</v>
       </c>
       <c r="F43" t="str">
         <v>Khối 1</v>
@@ -9198,13 +9198,13 @@
         <v>CS2</v>
       </c>
       <c r="C44" t="str">
-        <v>HS083</v>
+        <v>0701020104</v>
       </c>
       <c r="D44" t="str">
         <v>Nguyễn Thanh Phúc</v>
       </c>
       <c r="E44" t="str">
-        <v>Chưa rõ</v>
+        <v>1.2INT_CS2</v>
       </c>
       <c r="F44" t="str">
         <v>Khối 1</v>
@@ -9233,13 +9233,13 @@
         <v>CS2</v>
       </c>
       <c r="C45" t="str">
-        <v>HS286</v>
+        <v>0601021794</v>
       </c>
       <c r="D45" t="str">
         <v>ĐỖ NGUYỄN AN KHÔI</v>
       </c>
       <c r="E45" t="str">
-        <v>Chưa rõ</v>
+        <v>1.3_CS2</v>
       </c>
       <c r="F45" t="str">
         <v>Khối 1</v>
@@ -9268,13 +9268,13 @@
         <v>CS2</v>
       </c>
       <c r="C46" t="str">
-        <v>HS701020036</v>
+        <v>0601021828</v>
       </c>
       <c r="D46" t="str">
         <v>Phan Hải Đăng</v>
       </c>
       <c r="E46" t="str">
-        <v>Chưa rõ</v>
+        <v>1.3_CS2</v>
       </c>
       <c r="F46" t="str">
         <v>Khối 1</v>
@@ -9303,7 +9303,7 @@
         <v>CS2</v>
       </c>
       <c r="C47" t="str">
-        <v>HS701020095</v>
+        <v>0601012037</v>
       </c>
       <c r="D47" t="str">
         <v>Hoàng Bữu Minh Hưng</v>
@@ -9338,13 +9338,13 @@
         <v>CS2</v>
       </c>
       <c r="C48" t="str">
-        <v>HS701020105</v>
+        <v>0601021795</v>
       </c>
       <c r="D48" t="str">
         <v>Lê Hồ Duy Khang</v>
       </c>
       <c r="E48" t="str">
-        <v>Chưa rõ</v>
+        <v>1.3_CS2</v>
       </c>
       <c r="F48" t="str">
         <v>Khối 1</v>
@@ -9373,13 +9373,13 @@
         <v>CS2</v>
       </c>
       <c r="C49" t="str">
-        <v>HS701020188</v>
+        <v>0701020109</v>
       </c>
       <c r="D49" t="str">
         <v>Sangadziev Aron</v>
       </c>
       <c r="E49" t="str">
-        <v>Chưa rõ</v>
+        <v>1.2INT_CS2</v>
       </c>
       <c r="F49" t="str">
         <v>Khối 1</v>
@@ -9408,7 +9408,7 @@
         <v>CS3</v>
       </c>
       <c r="C50" t="str">
-        <v>HS148</v>
+        <v>0701030370</v>
       </c>
       <c r="D50" t="str">
         <v>Phan Anh Quân</v>
@@ -9443,7 +9443,7 @@
         <v>CS3</v>
       </c>
       <c r="C51" t="str">
-        <v>HS163</v>
+        <v>0701030387</v>
       </c>
       <c r="D51" t="str">
         <v>Đoàn Ngọc Thảo Chloe</v>
@@ -9478,7 +9478,7 @@
         <v>CS3</v>
       </c>
       <c r="C52" t="str">
-        <v>HS175</v>
+        <v>0501030625</v>
       </c>
       <c r="D52" t="str">
         <v>Hồ Hữu Bách</v>
@@ -9513,13 +9513,13 @@
         <v>CS3</v>
       </c>
       <c r="C53" t="str">
-        <v>HS701020076</v>
+        <v>0701030397</v>
       </c>
       <c r="D53" t="str">
         <v>Govorushko Mikhail</v>
       </c>
       <c r="E53" t="str">
-        <v>Chưa rõ</v>
+        <v>1.1INT_CS3</v>
       </c>
       <c r="F53" t="str">
         <v>Khối 1</v>
@@ -9548,7 +9548,7 @@
         <v>CS3</v>
       </c>
       <c r="C54" t="str">
-        <v>HS701020085</v>
+        <v>0701030402</v>
       </c>
       <c r="D54" t="str">
         <v>Lecomte Mailys Mộc Yên</v>
@@ -9583,7 +9583,7 @@
         <v>CS3</v>
       </c>
       <c r="C55" t="str">
-        <v>HS701020094</v>
+        <v>0701030384</v>
       </c>
       <c r="D55" t="str">
         <v>Hà Minh Khuê</v>
@@ -9618,7 +9618,7 @@
         <v>CS3</v>
       </c>
       <c r="C56" t="str">
-        <v>HS701020184</v>
+        <v>0701030415</v>
       </c>
       <c r="D56" t="str">
         <v>Phùng Đức Thiên Ân</v>
@@ -9653,7 +9653,7 @@
         <v>CS3</v>
       </c>
       <c r="C57" t="str">
-        <v>HS701020185</v>
+        <v>0701030416</v>
       </c>
       <c r="D57" t="str">
         <v>Phùng Chí Nam Anh</v>
@@ -9688,7 +9688,7 @@
         <v>CS4</v>
       </c>
       <c r="C58" t="str">
-        <v>HS179</v>
+        <v>0602040593</v>
       </c>
       <c r="D58" t="str">
         <v>Ayesha Mirza</v>
@@ -9723,7 +9723,7 @@
         <v>CS4</v>
       </c>
       <c r="C59" t="str">
-        <v>HS276</v>
+        <v>0602040630</v>
       </c>
       <c r="D59" t="str">
         <v>HÀ ĐẶNG BẢO NGỌC</v>
@@ -9758,7 +9758,7 @@
         <v>CS4</v>
       </c>
       <c r="C60" t="str">
-        <v>HS283</v>
+        <v>0601012397</v>
       </c>
       <c r="D60" t="str">
         <v>Nguyễn Thị Thu Thúy</v>
@@ -9793,7 +9793,7 @@
         <v>CS4</v>
       </c>
       <c r="C61" t="str">
-        <v>HS293</v>
+        <v>0602040636</v>
       </c>
       <c r="D61" t="str">
         <v>Huỳnh Hoàng An</v>
@@ -9828,7 +9828,7 @@
         <v>CS4</v>
       </c>
       <c r="C62" t="str">
-        <v>HS701020029</v>
+        <v>0602040624</v>
       </c>
       <c r="D62" t="str">
         <v>Đặng Ngọc Bảo Ngân</v>
@@ -9863,7 +9863,7 @@
         <v>CS4</v>
       </c>
       <c r="C63" t="str">
-        <v>HS701020030</v>
+        <v>0602040623</v>
       </c>
       <c r="D63" t="str">
         <v>Ngô Nhật Khang</v>
@@ -9898,7 +9898,7 @@
         <v>CS4</v>
       </c>
       <c r="C64" t="str">
-        <v>HS701020033</v>
+        <v>0602040522</v>
       </c>
       <c r="D64" t="str">
         <v>Võ Hoàng Vi</v>
@@ -9933,7 +9933,7 @@
         <v>CS4</v>
       </c>
       <c r="C65" t="str">
-        <v>HS701020061</v>
+        <v>0602040642</v>
       </c>
       <c r="D65" t="str">
         <v>Võ Như Quỳnh</v>
@@ -9968,7 +9968,7 @@
         <v>CS4</v>
       </c>
       <c r="C66" t="str">
-        <v>HS701020064</v>
+        <v>0602040613</v>
       </c>
       <c r="D66" t="str">
         <v>Đỗ Thành Nguyên</v>
@@ -10003,7 +10003,7 @@
         <v>CS4</v>
       </c>
       <c r="C67" t="str">
-        <v>HS701020065</v>
+        <v>0602040586</v>
       </c>
       <c r="D67" t="str">
         <v>Phạm Kiều Anh</v>
@@ -10038,7 +10038,7 @@
         <v>CS4</v>
       </c>
       <c r="C68" t="str">
-        <v>HS202</v>
+        <v>0602040621</v>
       </c>
       <c r="D68" t="str">
         <v>Võ Thị Anh Thư</v>
@@ -10073,13 +10073,13 @@
         <v>CS4</v>
       </c>
       <c r="C69" t="str">
-        <v>HS701020195</v>
+        <v>0602040655</v>
       </c>
       <c r="D69" t="str">
         <v>Ngô Huỳnh Anh Minh</v>
       </c>
       <c r="E69" t="str">
-        <v>Chưa rõ</v>
+        <v>6S_CS4</v>
       </c>
       <c r="F69" t="str">
         <v>Khối 6</v>
@@ -10108,7 +10108,7 @@
         <v>CS5</v>
       </c>
       <c r="C70" t="str">
-        <v>HS218</v>
+        <v>0601051095</v>
       </c>
       <c r="D70" t="str">
         <v>Mai Minh Minh</v>
@@ -10143,7 +10143,7 @@
         <v>CS5</v>
       </c>
       <c r="C71" t="str">
-        <v>HS240</v>
+        <v>0601051137</v>
       </c>
       <c r="D71" t="str">
         <v>Lâm Minh Khang</v>
@@ -10178,7 +10178,7 @@
         <v>CS5</v>
       </c>
       <c r="C72" t="str">
-        <v>HS334</v>
+        <v>0601051161</v>
       </c>
       <c r="D72" t="str">
         <v>Đặng Ái Thiên Vân</v>
@@ -10248,7 +10248,7 @@
         <v>CS5</v>
       </c>
       <c r="C74" t="str">
-        <v>HS132</v>
+        <v>0701030326</v>
       </c>
       <c r="D74" t="str">
         <v>Phạm Gia Hưng</v>
@@ -10283,13 +10283,13 @@
         <v>CS5</v>
       </c>
       <c r="C75" t="str">
-        <v>HS701020154</v>
+        <v>0601051050</v>
       </c>
       <c r="D75" t="str">
         <v>Vũ Đức Thịnh</v>
       </c>
       <c r="E75" t="str">
-        <v>Chưa rõ</v>
+        <v>1.5_CS5</v>
       </c>
       <c r="F75" t="str">
         <v>Khối 1</v>
@@ -10318,7 +10318,7 @@
         <v>CS5</v>
       </c>
       <c r="C76" t="str">
-        <v>HS701020159</v>
+        <v>0501030605</v>
       </c>
       <c r="D76" t="str">
         <v>Nguyễn Minh Anh</v>
@@ -10353,7 +10353,7 @@
         <v>CS5</v>
       </c>
       <c r="C77" t="str">
-        <v>HS701020158</v>
+        <v>0601051037</v>
       </c>
       <c r="D77" t="str">
         <v>Đỗ Duy Khôi</v>
@@ -10388,7 +10388,7 @@
         <v>CS5</v>
       </c>
       <c r="C78" t="str">
-        <v>HS701020163</v>
+        <v>0601051152</v>
       </c>
       <c r="D78" t="str">
         <v>Lê Nguyễn Hoàng Bảo</v>
@@ -10423,7 +10423,7 @@
         <v>CS5</v>
       </c>
       <c r="C79" t="str">
-        <v>HS701020167</v>
+        <v>0701050069</v>
       </c>
       <c r="D79" t="str">
         <v>Nguyễn Hoàng Đạt</v>
@@ -10458,7 +10458,7 @@
         <v>CS5</v>
       </c>
       <c r="C80" t="str">
-        <v>HS701020170</v>
+        <v>0701050068</v>
       </c>
       <c r="D80" t="str">
         <v>Nguyễn Hoàng Phúc</v>
@@ -10493,7 +10493,7 @@
         <v>CS5</v>
       </c>
       <c r="C81" t="str">
-        <v>HS701020166</v>
+        <v>0701030411</v>
       </c>
       <c r="D81" t="str">
         <v>Trần Minh Huy</v>

--- a/Bao_Cao_Khao_Sat_Dau_Nam_va_76_HS_CKDV_2026.xlsx
+++ b/Bao_Cao_Khao_Sat_Dau_Nam_va_76_HS_CKDV_2026.xlsx
@@ -7,9 +7,8 @@
     <sheet name="Tieu_Hoc_Theo_CS" sheetId="2" r:id="rId2"/>
     <sheet name="THCS_Theo_CS" sheetId="3" r:id="rId3"/>
     <sheet name="THPT_Theo_CS" sheetId="4" r:id="rId4"/>
-    <sheet name="THPT_7_Mon_Tu_Chon_K12" sheetId="5" r:id="rId5"/>
-    <sheet name="HS_Chua_Du_Diem_KSDV" sheetId="6" r:id="rId6"/>
-    <sheet name="76_HS_CKDV" sheetId="7" r:id="rId7"/>
+    <sheet name="HS_Chua_Du_Diem_KSDV" sheetId="5" r:id="rId5"/>
+    <sheet name="76_HS_CKDV" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -484,10 +483,10 @@
         <v>89.0%</v>
       </c>
       <c r="I6">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J6" t="str">
-        <v>2.0%</v>
+        <v>1.9%</v>
       </c>
       <c r="K6">
         <v>2002</v>
@@ -522,10 +521,10 @@
         <v>85.2%</v>
       </c>
       <c r="I7">
-        <v>310</v>
+        <v>243</v>
       </c>
       <c r="J7" t="str">
-        <v>14.8%</v>
+        <v>11.6%</v>
       </c>
       <c r="K7">
         <v>838</v>
@@ -560,10 +559,10 @@
         <v>65.7%</v>
       </c>
       <c r="I8">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J8" t="str">
-        <v>34.3%</v>
+        <v>33.9%</v>
       </c>
       <c r="K8">
         <v>76</v>
@@ -598,10 +597,10 @@
         <v>85.2%</v>
       </c>
       <c r="I9">
-        <v>537</v>
+        <v>464</v>
       </c>
       <c r="J9" t="str">
-        <v>10.3%</v>
+        <v>8.9%</v>
       </c>
       <c r="K9">
         <v>2916</v>
@@ -1126,10 +1125,10 @@
         <v>57</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>3.5%</v>
+        <v>1.8%</v>
       </c>
       <c r="G13">
         <v>53</v>
@@ -1158,10 +1157,10 @@
         <v>60</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>3.3%</v>
+        <v>1.7%</v>
       </c>
       <c r="G14">
         <v>53</v>
@@ -1350,10 +1349,10 @@
         <v>720</v>
       </c>
       <c r="E20">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F20" t="str">
-        <v>1.8%</v>
+        <v>1.5%</v>
       </c>
       <c r="G20">
         <v>646</v>
@@ -2810,10 +2809,10 @@
         <v>44</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" t="str">
-        <v>2.3%</v>
+        <v>0.0%</v>
       </c>
       <c r="G73">
         <v>40</v>
@@ -3130,10 +3129,10 @@
         <v>49</v>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="str">
-        <v>2.0%</v>
+        <v>0.0%</v>
       </c>
       <c r="G83">
         <v>37</v>
@@ -3354,10 +3353,10 @@
         <v>697</v>
       </c>
       <c r="E90">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F90" t="str">
-        <v>2.2%</v>
+        <v>1.9%</v>
       </c>
       <c r="G90">
         <v>609</v>
@@ -3386,10 +3385,10 @@
         <v>2624</v>
       </c>
       <c r="E92">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F92" t="str">
-        <v>2.0%</v>
+        <v>1.9%</v>
       </c>
       <c r="G92">
         <v>2335</v>
@@ -3482,10 +3481,10 @@
         <v>2.8%</v>
       </c>
       <c r="G6">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" t="str">
-        <v>94.4%</v>
+        <v>97.2%</v>
       </c>
       <c r="I6">
         <v>45</v>
@@ -3508,16 +3507,16 @@
         <v>99</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>3.0%</v>
+        <v>2.0%</v>
       </c>
       <c r="G7">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H7" t="str">
-        <v>89.9%</v>
+        <v>97.0%</v>
       </c>
       <c r="I7">
         <v>68</v>
@@ -3546,10 +3545,10 @@
         <v>37.5%</v>
       </c>
       <c r="G8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H8" t="str">
-        <v>39.1%</v>
+        <v>62.5%</v>
       </c>
       <c r="I8">
         <v>3</v>
@@ -3578,10 +3577,10 @@
         <v>14.7%</v>
       </c>
       <c r="G9">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="H9" t="str">
-        <v>73.5%</v>
+        <v>85.3%</v>
       </c>
       <c r="I9">
         <v>50</v>
@@ -3610,10 +3609,10 @@
         <v>1.4%</v>
       </c>
       <c r="G10">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H10" t="str">
-        <v>95.8%</v>
+        <v>98.6%</v>
       </c>
       <c r="I10">
         <v>37</v>
@@ -3642,10 +3641,10 @@
         <v>10.2%</v>
       </c>
       <c r="G11">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H11" t="str">
-        <v>79.6%</v>
+        <v>89.8%</v>
       </c>
       <c r="I11">
         <v>35</v>
@@ -3674,10 +3673,10 @@
         <v>1.5%</v>
       </c>
       <c r="G12">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H12" t="str">
-        <v>87.7%</v>
+        <v>98.5%</v>
       </c>
       <c r="I12">
         <v>27</v>
@@ -3706,10 +3705,10 @@
         <v>16.8%</v>
       </c>
       <c r="G13">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H13" t="str">
-        <v>72.3%</v>
+        <v>83.2%</v>
       </c>
       <c r="I13">
         <v>28</v>
@@ -3738,10 +3737,10 @@
         <v>6.9%</v>
       </c>
       <c r="G14">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H14" t="str">
-        <v>81.9%</v>
+        <v>93.1%</v>
       </c>
       <c r="I14">
         <v>44</v>
@@ -3770,10 +3769,10 @@
         <v>13.4%</v>
       </c>
       <c r="G15">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H15" t="str">
-        <v>75.3%</v>
+        <v>86.6%</v>
       </c>
       <c r="I15">
         <v>40</v>
@@ -3802,10 +3801,10 @@
         <v>15.6%</v>
       </c>
       <c r="G16">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H16" t="str">
-        <v>70.3%</v>
+        <v>84.4%</v>
       </c>
       <c r="I16">
         <v>19</v>
@@ -3834,10 +3833,10 @@
         <v>12.7%</v>
       </c>
       <c r="G17">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H17" t="str">
-        <v>82.4%</v>
+        <v>87.3%</v>
       </c>
       <c r="I17">
         <v>55</v>
@@ -3860,16 +3859,16 @@
         <v>1008</v>
       </c>
       <c r="E18">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F18" t="str">
-        <v>11.3%</v>
+        <v>11.2%</v>
       </c>
       <c r="G18">
-        <v>795</v>
+        <v>894</v>
       </c>
       <c r="H18" t="str">
-        <v>78.9%</v>
+        <v>88.7%</v>
       </c>
       <c r="I18">
         <v>451</v>
@@ -3929,10 +3928,10 @@
         <v>39</v>
       </c>
       <c r="E22">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>53.8%</v>
+        <v>2.6%</v>
       </c>
       <c r="G22">
         <v>18</v>
@@ -3961,10 +3960,10 @@
         <v>46</v>
       </c>
       <c r="E23">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F23" t="str">
-        <v>100.0%</v>
+        <v>0.0%</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3999,10 +3998,10 @@
         <v>18.2%</v>
       </c>
       <c r="G24">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H24" t="str">
-        <v>66.7%</v>
+        <v>81.8%</v>
       </c>
       <c r="I24">
         <v>5</v>
@@ -4031,10 +4030,10 @@
         <v>15.0%</v>
       </c>
       <c r="G25">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H25" t="str">
-        <v>45.0%</v>
+        <v>85.0%</v>
       </c>
       <c r="I25">
         <v>7</v>
@@ -4063,10 +4062,10 @@
         <v>2.6%</v>
       </c>
       <c r="G26">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H26" t="str">
-        <v>89.7%</v>
+        <v>97.4%</v>
       </c>
       <c r="I26">
         <v>27</v>
@@ -4095,10 +4094,10 @@
         <v>4.3%</v>
       </c>
       <c r="G27">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H27" t="str">
-        <v>87.0%</v>
+        <v>95.7%</v>
       </c>
       <c r="I27">
         <v>21</v>
@@ -4159,10 +4158,10 @@
         <v>0.0%</v>
       </c>
       <c r="G29">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H29" t="str">
-        <v>92.3%</v>
+        <v>100.0%</v>
       </c>
       <c r="I29">
         <v>16</v>
@@ -4191,10 +4190,10 @@
         <v>2.2%</v>
       </c>
       <c r="G30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H30" t="str">
-        <v>89.1%</v>
+        <v>97.8%</v>
       </c>
       <c r="I30">
         <v>28</v>
@@ -4223,10 +4222,10 @@
         <v>21.2%</v>
       </c>
       <c r="G31">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H31" t="str">
-        <v>69.7%</v>
+        <v>78.8%</v>
       </c>
       <c r="I31">
         <v>9</v>
@@ -4255,10 +4254,10 @@
         <v>0.0%</v>
       </c>
       <c r="G32">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H32" t="str">
-        <v>85.0%</v>
+        <v>100.0%</v>
       </c>
       <c r="I32">
         <v>15</v>
@@ -4319,10 +4318,10 @@
         <v>10.9%</v>
       </c>
       <c r="G34">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H34" t="str">
-        <v>54.3%</v>
+        <v>89.1%</v>
       </c>
       <c r="I34">
         <v>9</v>
@@ -4351,10 +4350,10 @@
         <v>6.1%</v>
       </c>
       <c r="G35">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H35" t="str">
-        <v>75.8%</v>
+        <v>93.9%</v>
       </c>
       <c r="I35">
         <v>11</v>
@@ -4377,16 +4376,16 @@
         <v>559</v>
       </c>
       <c r="E36">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="F36" t="str">
-        <v>17.4%</v>
+        <v>5.5%</v>
       </c>
       <c r="G36">
-        <v>396</v>
+        <v>462</v>
       </c>
       <c r="H36" t="str">
-        <v>70.8%</v>
+        <v>82.6%</v>
       </c>
       <c r="I36">
         <v>211</v>
@@ -4452,10 +4451,10 @@
         <v>16.7%</v>
       </c>
       <c r="G40">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H40" t="str">
-        <v>72.2%</v>
+        <v>83.3%</v>
       </c>
       <c r="I40">
         <v>10</v>
@@ -4516,10 +4515,10 @@
         <v>78.6%</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" t="str">
-        <v>14.3%</v>
+        <v>21.4%</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -4548,10 +4547,10 @@
         <v>25.0%</v>
       </c>
       <c r="G43">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H43" t="str">
-        <v>68.8%</v>
+        <v>75.0%</v>
       </c>
       <c r="I43">
         <v>3</v>
@@ -4580,10 +4579,10 @@
         <v>21.1%</v>
       </c>
       <c r="G44">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H44" t="str">
-        <v>52.6%</v>
+        <v>78.9%</v>
       </c>
       <c r="I44">
         <v>1</v>
@@ -4612,10 +4611,10 @@
         <v>0.0%</v>
       </c>
       <c r="G45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H45" t="str">
-        <v>90.0%</v>
+        <v>100.0%</v>
       </c>
       <c r="I45">
         <v>5</v>
@@ -4676,10 +4675,10 @@
         <v>37.5%</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H47" t="str">
-        <v>31.3%</v>
+        <v>62.5%</v>
       </c>
       <c r="I47">
         <v>2</v>
@@ -4708,10 +4707,10 @@
         <v>42.1%</v>
       </c>
       <c r="G48">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H48" t="str">
-        <v>52.6%</v>
+        <v>57.9%</v>
       </c>
       <c r="I48">
         <v>1</v>
@@ -4740,10 +4739,10 @@
         <v>30.0%</v>
       </c>
       <c r="G49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H49" t="str">
-        <v>60.0%</v>
+        <v>70.0%</v>
       </c>
       <c r="I49">
         <v>2</v>
@@ -4772,10 +4771,10 @@
         <v>7.1%</v>
       </c>
       <c r="G50">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H50" t="str">
-        <v>78.6%</v>
+        <v>92.9%</v>
       </c>
       <c r="I50">
         <v>6</v>
@@ -4804,10 +4803,10 @@
         <v>25.0%</v>
       </c>
       <c r="G51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H51" t="str">
-        <v>68.8%</v>
+        <v>75.0%</v>
       </c>
       <c r="I51">
         <v>8</v>
@@ -4836,10 +4835,10 @@
         <v>27.8%</v>
       </c>
       <c r="G52">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="H52" t="str">
-        <v>60.8%</v>
+        <v>72.2%</v>
       </c>
       <c r="I52">
         <v>44</v>
@@ -4905,10 +4904,10 @@
         <v>24.4%</v>
       </c>
       <c r="G56">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H56" t="str">
-        <v>68.9%</v>
+        <v>75.6%</v>
       </c>
       <c r="I56">
         <v>20</v>
@@ -4969,10 +4968,10 @@
         <v>43.5%</v>
       </c>
       <c r="G58">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H58" t="str">
-        <v>39.1%</v>
+        <v>56.5%</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -5001,10 +5000,10 @@
         <v>0.0%</v>
       </c>
       <c r="G59">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H59" t="str">
-        <v>88.9%</v>
+        <v>100.0%</v>
       </c>
       <c r="I59">
         <v>10</v>
@@ -5033,10 +5032,10 @@
         <v>2.2%</v>
       </c>
       <c r="G60">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H60" t="str">
-        <v>95.6%</v>
+        <v>97.8%</v>
       </c>
       <c r="I60">
         <v>22</v>
@@ -5065,10 +5064,10 @@
         <v>3.2%</v>
       </c>
       <c r="G61">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H61" t="str">
-        <v>87.1%</v>
+        <v>96.8%</v>
       </c>
       <c r="I61">
         <v>6</v>
@@ -5097,10 +5096,10 @@
         <v>17.4%</v>
       </c>
       <c r="G62">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H62" t="str">
-        <v>73.9%</v>
+        <v>82.6%</v>
       </c>
       <c r="I62">
         <v>4</v>
@@ -5129,10 +5128,10 @@
         <v>5.6%</v>
       </c>
       <c r="G63">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H63" t="str">
-        <v>88.9%</v>
+        <v>94.4%</v>
       </c>
       <c r="I63">
         <v>6</v>
@@ -5161,10 +5160,10 @@
         <v>17.8%</v>
       </c>
       <c r="G64">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H64" t="str">
-        <v>66.7%</v>
+        <v>82.2%</v>
       </c>
       <c r="I64">
         <v>20</v>
@@ -5193,10 +5192,10 @@
         <v>15.6%</v>
       </c>
       <c r="G65">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H65" t="str">
-        <v>78.1%</v>
+        <v>84.4%</v>
       </c>
       <c r="I65">
         <v>15</v>
@@ -5225,10 +5224,10 @@
         <v>26.1%</v>
       </c>
       <c r="G66">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H66" t="str">
-        <v>52.2%</v>
+        <v>73.9%</v>
       </c>
       <c r="I66">
         <v>3</v>
@@ -5257,10 +5256,10 @@
         <v>16.7%</v>
       </c>
       <c r="G67">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H67" t="str">
-        <v>72.2%</v>
+        <v>83.3%</v>
       </c>
       <c r="I67">
         <v>6</v>
@@ -5289,10 +5288,10 @@
         <v>14.2%</v>
       </c>
       <c r="G68">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="H68" t="str">
-        <v>76.7%</v>
+        <v>85.8%</v>
       </c>
       <c r="I68">
         <v>132</v>
@@ -5315,16 +5314,16 @@
         <v>2095</v>
       </c>
       <c r="E70">
-        <v>310</v>
+        <v>243</v>
       </c>
       <c r="F70" t="str">
-        <v>14.8%</v>
+        <v>11.6%</v>
       </c>
       <c r="G70">
-        <v>1568</v>
+        <v>1785</v>
       </c>
       <c r="H70" t="str">
-        <v>74.8%</v>
+        <v>85.2%</v>
       </c>
       <c r="I70">
         <v>838</v>
@@ -5411,10 +5410,10 @@
         <v>20.9%</v>
       </c>
       <c r="G6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H6" t="str">
-        <v>72.1%</v>
+        <v>79.1%</v>
       </c>
       <c r="I6">
         <v>13</v>
@@ -5443,10 +5442,10 @@
         <v>82.4%</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="str">
-        <v>5.9%</v>
+        <v>17.6%</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5475,10 +5474,10 @@
         <v>17.4%</v>
       </c>
       <c r="G8">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H8" t="str">
-        <v>58.7%</v>
+        <v>82.6%</v>
       </c>
       <c r="I8">
         <v>5</v>
@@ -5507,10 +5506,10 @@
         <v>32.5%</v>
       </c>
       <c r="G9">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H9" t="str">
-        <v>40.0%</v>
+        <v>67.5%</v>
       </c>
       <c r="I9">
         <v>3</v>
@@ -5539,10 +5538,10 @@
         <v>82.4%</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="str">
-        <v>0.0%</v>
+        <v>17.6%</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -5571,10 +5570,10 @@
         <v>38.6%</v>
       </c>
       <c r="G11">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H11" t="str">
-        <v>31.8%</v>
+        <v>61.4%</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -5597,16 +5596,16 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F12" t="str">
-        <v>34.9%</v>
+        <v>30.2%</v>
       </c>
       <c r="G12">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H12" t="str">
-        <v>58.1%</v>
+        <v>65.1%</v>
       </c>
       <c r="I12">
         <v>11</v>
@@ -5635,10 +5634,10 @@
         <v>35.3%</v>
       </c>
       <c r="G13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H13" t="str">
-        <v>41.2%</v>
+        <v>64.7%</v>
       </c>
       <c r="I13">
         <v>3</v>
@@ -5667,10 +5666,10 @@
         <v>26.1%</v>
       </c>
       <c r="G14">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="H14" t="str">
-        <v>47.8%</v>
+        <v>73.9%</v>
       </c>
       <c r="I14">
         <v>4</v>
@@ -5795,10 +5794,10 @@
         <v>16.7%</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H18" t="str">
-        <v>33.3%</v>
+        <v>83.3%</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -5891,10 +5890,10 @@
         <v>60.7%</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H21" t="str">
-        <v>14.3%</v>
+        <v>39.3%</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -5917,16 +5916,16 @@
         <v>370</v>
       </c>
       <c r="E22">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F22" t="str">
-        <v>36.5%</v>
+        <v>35.9%</v>
       </c>
       <c r="G22">
-        <v>163</v>
+        <v>235</v>
       </c>
       <c r="H22" t="str">
-        <v>44.1%</v>
+        <v>63.5%</v>
       </c>
       <c r="I22">
         <v>46</v>
@@ -5992,10 +5991,10 @@
         <v>0.0%</v>
       </c>
       <c r="G26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H26" t="str">
-        <v>85.7%</v>
+        <v>100.0%</v>
       </c>
       <c r="I26">
         <v>4</v>
@@ -6024,10 +6023,10 @@
         <v>18.2%</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H27" t="str">
-        <v>45.5%</v>
+        <v>81.8%</v>
       </c>
       <c r="I27">
         <v>2</v>
@@ -6056,10 +6055,10 @@
         <v>0.0%</v>
       </c>
       <c r="G28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" t="str">
-        <v>85.7%</v>
+        <v>100.0%</v>
       </c>
       <c r="I28">
         <v>5</v>
@@ -6088,10 +6087,10 @@
         <v>0.0%</v>
       </c>
       <c r="G29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H29" t="str">
-        <v>85.7%</v>
+        <v>100.0%</v>
       </c>
       <c r="I29">
         <v>2</v>
@@ -6120,10 +6119,10 @@
         <v>27.3%</v>
       </c>
       <c r="G30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H30" t="str">
-        <v>63.6%</v>
+        <v>72.7%</v>
       </c>
       <c r="I30">
         <v>1</v>
@@ -6152,10 +6151,10 @@
         <v>28.6%</v>
       </c>
       <c r="G31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" t="str">
-        <v>57.1%</v>
+        <v>71.4%</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -6184,10 +6183,10 @@
         <v>0.0%</v>
       </c>
       <c r="G32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H32" t="str">
-        <v>85.7%</v>
+        <v>100.0%</v>
       </c>
       <c r="I32">
         <v>2</v>
@@ -6248,10 +6247,10 @@
         <v>0.0%</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H34" t="str">
-        <v>85.7%</v>
+        <v>100.0%</v>
       </c>
       <c r="I34">
         <v>4</v>
@@ -6344,10 +6343,10 @@
         <v>0.0%</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" t="str">
-        <v>50.0%</v>
+        <v>100.0%</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -6408,10 +6407,10 @@
         <v>9.6%</v>
       </c>
       <c r="G39">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="H39" t="str">
-        <v>75.9%</v>
+        <v>90.4%</v>
       </c>
       <c r="I39">
         <v>28</v>
@@ -6477,10 +6476,10 @@
         <v>80.0%</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" t="str">
-        <v>10.0%</v>
+        <v>20.0%</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -6509,10 +6508,10 @@
         <v>14.3%</v>
       </c>
       <c r="G44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H44" t="str">
-        <v>71.4%</v>
+        <v>85.7%</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -6541,10 +6540,10 @@
         <v>55.6%</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H45" t="str">
-        <v>11.1%</v>
+        <v>44.4%</v>
       </c>
       <c r="I45">
         <v>1</v>
@@ -6573,10 +6572,10 @@
         <v>57.1%</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" t="str">
-        <v>28.6%</v>
+        <v>42.9%</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -6637,10 +6636,10 @@
         <v>42.9%</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H48" t="str">
-        <v>42.9%</v>
+        <v>57.1%</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -6733,10 +6732,10 @@
         <v>56.4%</v>
       </c>
       <c r="G51">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H51" t="str">
-        <v>30.9%</v>
+        <v>43.6%</v>
       </c>
       <c r="I51">
         <v>2</v>
@@ -6759,16 +6758,16 @@
         <v>508</v>
       </c>
       <c r="E53">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F53" t="str">
-        <v>34.3%</v>
+        <v>33.9%</v>
       </c>
       <c r="G53">
-        <v>243</v>
+        <v>334</v>
       </c>
       <c r="H53" t="str">
-        <v>47.8%</v>
+        <v>65.7%</v>
       </c>
       <c r="I53">
         <v>76</v>
@@ -6786,342 +6785,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>THỐNG KÊ CHI TIẾT 7 MÔN TỰ CHỌN KHỐI 12 THEO CƠ SỞ (NGOÀI TOÁN - VĂN - ANH)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>* Áp dụng cho học sinh Khối 12 làm bài khảo sát định hướng tốt nghiệp THPT theo tổ hợp môn</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>STT</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Cơ sở</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Môn học tự chọn</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Khối lớp</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Số HS khảo sát</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Điểm dưới TB (&lt; 5.0)</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Tỷ lệ &lt; 5.0</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Điểm Chuẩn (≥ 5.0)</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Tỷ lệ Đạt chuẩn</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Điểm 8 đến 10 (Giỏi)</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Tỷ lệ Giỏi</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Vật lí</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Khối 12</v>
-      </c>
-      <c r="E5">
-        <v>13</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5" t="str">
-        <v>15.4%</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5" t="str">
-        <v>84.6%</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5" t="str">
-        <v>15.4%</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Hóa học</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Khối 12</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6" t="str">
-        <v>36.4%</v>
-      </c>
-      <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6" t="str">
-        <v>63.6%</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6" t="str">
-        <v>18.2%</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Sinh học</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Khối 12</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" t="str">
-        <v>0.0%</v>
-      </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7" t="str">
-        <v>100.0%</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7" t="str">
-        <v>30.0%</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>4</v>
-      </c>
-      <c r="B8" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Lịch sử</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Khối 12</v>
-      </c>
-      <c r="E8">
-        <v>11</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-      <c r="G8" t="str">
-        <v>45.5%</v>
-      </c>
-      <c r="H8">
-        <v>6</v>
-      </c>
-      <c r="I8" t="str">
-        <v>54.5%</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" t="str">
-        <v>0.0%</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>5</v>
-      </c>
-      <c r="B9" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Địa lí</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Khối 12</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" t="str">
-        <v>0.0%</v>
-      </c>
-      <c r="H9">
-        <v>11</v>
-      </c>
-      <c r="I9" t="str">
-        <v>100.0%</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-      <c r="K9" t="str">
-        <v>18.2%</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>6</v>
-      </c>
-      <c r="B10" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C10" t="str">
-        <v>GD Kinh tế &amp; Pháp luật</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Khối 12</v>
-      </c>
-      <c r="E10">
-        <v>11</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" t="str">
-        <v>0.0%</v>
-      </c>
-      <c r="H10">
-        <v>11</v>
-      </c>
-      <c r="I10" t="str">
-        <v>100.0%</v>
-      </c>
-      <c r="J10">
-        <v>3</v>
-      </c>
-      <c r="K10" t="str">
-        <v>27.3%</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>7</v>
-      </c>
-      <c r="B11" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Tin học / ICT</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Khối 12</v>
-      </c>
-      <c r="E11">
-        <v>4</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="str">
-        <v>25.0%</v>
-      </c>
-      <c r="H11">
-        <v>3</v>
-      </c>
-      <c r="I11" t="str">
-        <v>75.0%</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" t="str">
-        <v>0.0%</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>-</v>
-      </c>
-      <c r="B12" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C12" t="str">
-        <v>TỔNG 7 MÔN TỰ CHỌN K12</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Khối 12</v>
-      </c>
-      <c r="E12">
-        <v>71</v>
-      </c>
-      <c r="F12">
-        <v>12</v>
-      </c>
-      <c r="G12" t="str">
-        <v>16.9%</v>
-      </c>
-      <c r="H12">
-        <v>59</v>
-      </c>
-      <c r="I12" t="str">
-        <v>83.1%</v>
-      </c>
-      <c r="J12">
-        <v>12</v>
-      </c>
-      <c r="K12" t="str">
-        <v>16.9%</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K12"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K22"/>
   <sheetData>
     <row r="1">
@@ -7806,7 +7469,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K81"/>
   <sheetData>

--- a/Bao_Cao_Khao_Sat_Dau_Nam_va_76_HS_CKDV_2026.xlsx
+++ b/Bao_Cao_Khao_Sat_Dau_Nam_va_76_HS_CKDV_2026.xlsx
@@ -7,8 +7,7 @@
     <sheet name="Tieu_Hoc_Theo_CS" sheetId="2" r:id="rId2"/>
     <sheet name="THCS_Theo_CS" sheetId="3" r:id="rId3"/>
     <sheet name="THPT_Theo_CS" sheetId="4" r:id="rId4"/>
-    <sheet name="HS_Chua_Du_Diem_KSDV" sheetId="5" r:id="rId5"/>
-    <sheet name="76_HS_CKDV" sheetId="6" r:id="rId6"/>
+    <sheet name="76_HS_CKDV" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -6785,3407 +6784,3536 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:I134"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>BẢNG THỐNG KÊ CHI TIẾT HỌC SINH CKĐV CHƯA CÓ ĐIỂM KSĐV HOẶC THIẾU MÔN CAM KẾT</v>
+        <v>BẢNG MAP ĐIỂM KHẢO SÁT ĐẦU VÀO (KSĐV) VS KHẢO SÁT ĐẦU NĂM (KSĐN) 76 HỌC SINH CKĐV NHẬP HỌC</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>* Tổng số: 18 học sinh (gồm 3 HS chưa có điểm, 11 HS thiếu môn CK, 4 HS cam kết tâm lý)</v>
+        <v>* Quy chuẩn Tiến bộ: Với Tiểu học, Điểm KSĐN phải Đạt từ 5.0 trở lên mới tính là Tiến bộ, nhưng không đạt chuẩn.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>* Quy chuẩn Đạt chuẩn: Tiểu học điểm ≥ 7.0; THCS &amp; THPT điểm ≥ 5.0.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>* HS khảo sát lại: Tổng hợp hiển thị đầy đủ các môn, môn khảo sát lại lấy kết quả cuối cùng.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>&gt;&gt;&gt; CƠ SỞ: CS1 (36 HỌC SINH CKĐV)</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
         <v>STT</v>
       </c>
-      <c r="B4" t="str">
-        <v>Cơ sở</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Mã HS</v>
-      </c>
-      <c r="D4" t="str">
+      <c r="B7" t="str">
         <v>Họ và tên</v>
       </c>
-      <c r="E4" t="str">
+      <c r="C7" t="str">
         <v>Lớp</v>
       </c>
-      <c r="F4" t="str">
+      <c r="D7" t="str">
         <v>Khối</v>
       </c>
-      <c r="G4" t="str">
-        <v>Môn Cam Kết</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Phân loại Tình trạng</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Điểm KSĐV Hiện Có</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Điểm KSĐN Thực Tế</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Nguyên nhân &amp; Căn cứ Tuyển sinh</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="str">
-        <v>CS2</v>
-      </c>
-      <c r="C5" t="str">
-        <v>0601021777</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Lê Gia Lân</v>
-      </c>
-      <c r="E5" t="str">
-        <v>1.3_CS2</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Khối 1</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Tâm lý</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Cam kết Tâm lý</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Anh: 2.3 (Tổng: 23.3)</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Chỉ cam kết theo dõi tâm lý lứa tuổi, không khảo sát văn hóa</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" t="str">
-        <v>CS2</v>
-      </c>
-      <c r="C6" t="str">
-        <v>0601021457</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Đào Trần Thảo Linh</v>
-      </c>
-      <c r="E6" t="str">
-        <v>1.3_CS2</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Khối 1</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Tâm lý, Tiếng Việt</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Cam kết Tâm lý</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Anh: 3.0 (Tổng: 30)</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K6" t="str">
-        <v>Chỉ cam kết theo dõi tâm lý lứa tuổi, không khảo sát văn hóa</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C7" t="str">
-        <v>0601011426</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Lê Nguyên Khang</v>
-      </c>
       <c r="E7" t="str">
-        <v>2.1_CS1</v>
+        <v>Môn CKĐV</v>
       </c>
       <c r="F7" t="str">
-        <v>Khối 2</v>
+        <v>Điểm KSĐV</v>
       </c>
       <c r="G7" t="str">
-        <v>Tiếng Anh</v>
+        <v>Điểm KSĐN</v>
       </c>
       <c r="H7" t="str">
-        <v>Chưa có điểm KSĐV</v>
+        <v>Tiến bộ</v>
       </c>
       <c r="I7" t="str">
-        <v>—</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Toán: 9; Tiếng Việt: 8; Anh: 7.9</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Diện Tuyển thẳng (không phải thi khảo sát đầu vào)</v>
+        <v>Đạt chuẩn</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Nguyễn Gia Bảo</v>
+      </c>
+      <c r="C8" t="str">
+        <v>9.2_CS1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Khối 9</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F8" t="str">
         <v>4</v>
       </c>
-      <c r="B8" t="str">
-        <v>CS3</v>
-      </c>
-      <c r="C8" t="str">
-        <v>0701030370</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Phan Anh Quân</v>
-      </c>
-      <c r="E8" t="str">
-        <v>9INT_CS3</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Khối 9</v>
-      </c>
       <c r="G8" t="str">
-        <v>Toán, Tiếng Anh</v>
+        <v>3.5</v>
       </c>
       <c r="H8" t="str">
-        <v>Thiếu môn CKĐV</v>
+        <v>Chưa tiến bộ</v>
       </c>
       <c r="I8" t="str">
-        <v>Ngữ Văn: 5; Anh: 4.1 (Tổng: 41)</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Toán: 6.25; Ngữ Văn: 6; Anh: 5.6</v>
-      </c>
-      <c r="K8" t="str">
-        <v>Hệ Quốc tế (chỉ thi EPT 41/100, không thi Toán đề chung)</v>
+        <v>Dưới TB</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>5</v>
+      <c r="A9" t="str">
+        <v/>
       </c>
       <c r="B9" t="str">
-        <v>CS3</v>
+        <v/>
       </c>
       <c r="C9" t="str">
-        <v>0701030387</v>
+        <v/>
       </c>
       <c r="D9" t="str">
-        <v>Đoàn Ngọc Thảo Chloe</v>
+        <v/>
       </c>
       <c r="E9" t="str">
-        <v>2.1INT_CS3</v>
+        <v>Tiếng Anh</v>
       </c>
       <c r="F9" t="str">
-        <v>Khối 2</v>
+        <v>1.0</v>
       </c>
       <c r="G9" t="str">
-        <v>Tiếng Việt, Tiếng Anh</v>
+        <v>8</v>
       </c>
       <c r="H9" t="str">
-        <v>Thiếu môn CKĐV</v>
+        <v>Bứt phá (+7)</v>
       </c>
       <c r="I9" t="str">
-        <v>Anh: 8.4 (Tổng: 84)</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Tiếng Việt: 4; Anh: 9.8</v>
-      </c>
-      <c r="K9" t="str">
-        <v>Học sinh nước ngoài / song ngữ (chưa qua khảo sát Tiếng Việt đầu vào)</v>
+        <v>Đạt chuẩn</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B10" t="str">
-        <v>CS1</v>
+        <v>Lê Nguyên Khang</v>
       </c>
       <c r="C10" t="str">
-        <v>0601011201</v>
+        <v>2.1_CS1</v>
       </c>
       <c r="D10" t="str">
-        <v>Mai Huy Thắng</v>
+        <v>Khối 2</v>
       </c>
       <c r="E10" t="str">
-        <v>7.1_CS1</v>
+        <v>Tiếng Anh</v>
       </c>
       <c r="F10" t="str">
-        <v>Khối 7</v>
+        <v>0.4</v>
       </c>
       <c r="G10" t="str">
-        <v>Toán</v>
+        <v>7.9</v>
       </c>
       <c r="H10" t="str">
-        <v>Thiếu môn CKĐV</v>
+        <v>Bứt phá (+7.5)</v>
       </c>
       <c r="I10" t="str">
-        <v>Ngữ Văn: 8; Anh: 8.0 (Tổng: 80)</v>
-      </c>
-      <c r="J10" t="str">
-        <v>Toán: 8; Ngữ Văn: 7; Anh: 8.8</v>
-      </c>
-      <c r="K10" t="str">
-        <v>Được bảo lưu/miễn thi Toán (đã có điểm Văn 8.0, Anh 8.0)</v>
+        <v>Đạt chuẩn</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B11" t="str">
-        <v>CS1</v>
+        <v>Phạm Nguyễn Minh Anh</v>
       </c>
       <c r="C11" t="str">
-        <v>0601012396</v>
+        <v>10.2_CS1</v>
       </c>
       <c r="D11" t="str">
-        <v xml:space="preserve">Trần Hoàng Anh </v>
+        <v>Khối 10</v>
       </c>
       <c r="E11" t="str">
-        <v>9.2_CS1</v>
+        <v>Tiếng Anh</v>
       </c>
       <c r="F11" t="str">
-        <v>Khối 9</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="str">
-        <v>Tiếng Anh, Toán</v>
+        <v>Chưa thi</v>
       </c>
       <c r="H11" t="str">
-        <v>Thiếu môn CKĐV</v>
+        <v>Chưa thi KSĐN</v>
       </c>
       <c r="I11" t="str">
-        <v>Toán: 4; Ngữ Văn: 6.5</v>
-      </c>
-      <c r="J11" t="str">
-        <v>Toán: 6.5; Ngữ Văn: 6; Anh: 4</v>
-      </c>
-      <c r="K11" t="str">
-        <v>Môn Tiếng Anh chưa nhập điểm trên hệ thống (đã có điểm Toán, Văn)</v>
+        <v>Chưa có bài KSĐN</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B12" t="str">
-        <v>CS1</v>
+        <v>Phan Đình Phùng</v>
       </c>
       <c r="C12" t="str">
-        <v>0601012393</v>
+        <v>10.1_CS1</v>
       </c>
       <c r="D12" t="str">
-        <v>Nguyễn Thanh Thảo</v>
+        <v>Khối 10</v>
       </c>
       <c r="E12" t="str">
-        <v>9.4_CS1</v>
+        <v>Tiếng Anh</v>
       </c>
       <c r="F12" t="str">
-        <v>Khối 9</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="str">
-        <v>Tiếng Anh</v>
+        <v>4.6</v>
       </c>
       <c r="H12" t="str">
-        <v>Chưa có điểm KSĐV</v>
+        <v>Tăng nhẹ (+3.1)</v>
       </c>
       <c r="I12" t="str">
-        <v>—</v>
-      </c>
-      <c r="J12" t="str">
-        <v>Toán: 5; Ngữ Văn: 5.5; Anh: 4.6</v>
-      </c>
-      <c r="K12" t="str">
-        <v>Chưa cập nhật điểm bài thi Tiếng Anh trên hệ thống</v>
+        <v>Dưới TB</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>9</v>
+      <c r="A13" t="str">
+        <v/>
       </c>
       <c r="B13" t="str">
-        <v>CS1</v>
+        <v/>
       </c>
       <c r="C13" t="str">
-        <v>0601011617</v>
+        <v/>
       </c>
       <c r="D13" t="str">
-        <v>Lê Khánh Hà</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v>10.2_CS1</v>
+        <v>Toán</v>
       </c>
       <c r="F13" t="str">
-        <v>Khối 10</v>
+        <v>4</v>
       </c>
       <c r="G13" t="str">
-        <v>Toán, Tiếng Anh</v>
+        <v>4.75</v>
       </c>
       <c r="H13" t="str">
-        <v>Thiếu môn CKĐV</v>
+        <v>Tăng nhẹ (+0.8)</v>
       </c>
       <c r="I13" t="str">
-        <v>Toán: 4; Ngữ Văn: 7</v>
-      </c>
-      <c r="J13" t="str">
-        <v>Toán: 7; Ngữ Văn: 4.5; Anh: 4</v>
-      </c>
-      <c r="K13" t="str">
-        <v>Môn Tiếng Anh chưa nhập điểm trên hệ thống (đã có điểm Toán, Văn)</v>
+        <v>Dưới TB</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>10</v>
+      <c r="A14" t="str">
+        <v/>
       </c>
       <c r="B14" t="str">
-        <v>CS1</v>
+        <v/>
       </c>
       <c r="C14" t="str">
-        <v>0601012399</v>
+        <v/>
       </c>
       <c r="D14" t="str">
-        <v>Ngô Thục Đan</v>
+        <v/>
       </c>
       <c r="E14" t="str">
-        <v>9.1_CS1</v>
+        <v>Ngữ Văn</v>
       </c>
       <c r="F14" t="str">
-        <v>Khối 9</v>
+        <v>3</v>
       </c>
       <c r="G14" t="str">
-        <v>Tâm lý</v>
+        <v>2</v>
       </c>
       <c r="H14" t="str">
-        <v>Cam kết Tâm lý</v>
+        <v>Chưa tiến bộ</v>
       </c>
       <c r="I14" t="str">
-        <v>Toán: 5; Anh: 6.5 (Tổng: 65)</v>
-      </c>
-      <c r="J14" t="str">
-        <v>Toán: 3; Ngữ Văn: 8.5; Anh: 7.5</v>
-      </c>
-      <c r="K14" t="str">
-        <v>Chỉ cam kết theo dõi tâm lý lứa tuổi, không khảo sát văn hóa</v>
+        <v>Dưới TB</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B15" t="str">
-        <v>CS2</v>
+        <v>Mai Huy Thắng</v>
       </c>
       <c r="C15" t="str">
-        <v>0601021828</v>
+        <v>7.1_CS1</v>
       </c>
       <c r="D15" t="str">
-        <v>Phan Hải Đăng</v>
+        <v>Khối 7</v>
       </c>
       <c r="E15" t="str">
-        <v>1.3_CS2</v>
+        <v>Toán</v>
       </c>
       <c r="F15" t="str">
-        <v>Khối 1</v>
+        <v>4.5</v>
       </c>
       <c r="G15" t="str">
-        <v>Chung / Theo dõi</v>
+        <v>8</v>
       </c>
       <c r="H15" t="str">
-        <v>Chưa có điểm KSĐV</v>
+        <v>Bứt phá (+3.5)</v>
       </c>
       <c r="I15" t="str">
-        <v>—</v>
-      </c>
-      <c r="J15" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K15" t="str">
-        <v>Cam kết theo dõi phát triển ngôn ngữ (chưa thi khảo sát văn hóa)</v>
+        <v>Đạt chuẩn</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B16" t="str">
-        <v>CS3</v>
+        <v xml:space="preserve">Phạm Thùy Gia Hân </v>
       </c>
       <c r="C16" t="str">
-        <v>0701030397</v>
+        <v>10.2_CS1</v>
       </c>
       <c r="D16" t="str">
-        <v>Govorushko Mikhail</v>
+        <v>Khối 10</v>
       </c>
       <c r="E16" t="str">
-        <v>1.1INT_CS3</v>
+        <v>Tiếng Anh</v>
       </c>
       <c r="F16" t="str">
-        <v>Khối 1</v>
+        <v>2.0</v>
       </c>
       <c r="G16" t="str">
-        <v>Tiếng Việt</v>
+        <v>4.7</v>
       </c>
       <c r="H16" t="str">
-        <v>Thiếu môn CKĐV</v>
+        <v>Tăng nhẹ (+2.7)</v>
       </c>
       <c r="I16" t="str">
-        <v>Anh: 3.2 (Tổng: 31.7)</v>
-      </c>
-      <c r="J16" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K16" t="str">
-        <v>Học sinh nước ngoài / song ngữ (chưa qua khảo sát Tiếng Việt đầu vào)</v>
+        <v>Dưới TB</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B17" t="str">
-        <v>CS3</v>
+        <v>Nguyễn Bình Phương An</v>
       </c>
       <c r="C17" t="str">
-        <v>0701030402</v>
+        <v>10.1_CS1</v>
       </c>
       <c r="D17" t="str">
-        <v>Lecomte Mailys Mộc Yên</v>
+        <v>Khối 10</v>
       </c>
       <c r="E17" t="str">
-        <v>4INT_CS3</v>
+        <v>Tiếng Anh</v>
       </c>
       <c r="F17" t="str">
-        <v>Khối 4</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="str">
-        <v>Tiếng Việt, Tiếng Anh</v>
+        <v>4.8</v>
       </c>
       <c r="H17" t="str">
-        <v>Thiếu môn CKĐV</v>
+        <v>Tăng nhẹ (+3.3)</v>
       </c>
       <c r="I17" t="str">
-        <v>Anh: 9.6 (Tổng: 96)</v>
-      </c>
-      <c r="J17" t="str">
-        <v>Tiếng Việt: 5; Anh: 7.3</v>
-      </c>
-      <c r="K17" t="str">
-        <v>Học sinh nước ngoài / song ngữ (chưa qua khảo sát Tiếng Việt đầu vào)</v>
+        <v>Dưới TB</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B18" t="str">
-        <v>CS4</v>
+        <v>Lê Bảo Trâm</v>
       </c>
       <c r="C18" t="str">
-        <v>0602040621</v>
+        <v>7.3_CS1</v>
       </c>
       <c r="D18" t="str">
-        <v>Võ Thị Anh Thư</v>
+        <v>Khối 7</v>
       </c>
       <c r="E18" t="str">
-        <v>7S_CS4</v>
+        <v>Tiếng Anh</v>
       </c>
       <c r="F18" t="str">
-        <v>Khối 7</v>
+        <v>4.2</v>
       </c>
       <c r="G18" t="str">
-        <v>Tiếng Anh</v>
+        <v>7.5</v>
       </c>
       <c r="H18" t="str">
-        <v>Thiếu môn CKĐV</v>
+        <v>Bứt phá (+3.3)</v>
       </c>
       <c r="I18" t="str">
-        <v>Toán: 8</v>
-      </c>
-      <c r="J18" t="str">
-        <v>Toán: 4.3; Ngữ Văn: 7.5; Anh: 2.6</v>
-      </c>
-      <c r="K18" t="str">
-        <v>Thi lại Toán đạt 8.0; môn Tiếng Anh chưa nhập điểm trên hệ thống</v>
+        <v>Đạt chuẩn</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B19" t="str">
-        <v>CS2</v>
+        <v>Lê Bảo Châu</v>
       </c>
       <c r="C19" t="str">
-        <v>0601021795</v>
+        <v>9.3_CS1</v>
       </c>
       <c r="D19" t="str">
-        <v>Lê Hồ Duy Khang</v>
+        <v>Khối 9</v>
       </c>
       <c r="E19" t="str">
-        <v>1.3_CS2</v>
+        <v>Toán</v>
       </c>
       <c r="F19" t="str">
-        <v>Khối 1</v>
+        <v>2</v>
       </c>
       <c r="G19" t="str">
-        <v>Tâm lý</v>
+        <v>3.5</v>
       </c>
       <c r="H19" t="str">
-        <v>Cam kết Tâm lý</v>
+        <v>Tăng nhẹ (+1.5)</v>
       </c>
       <c r="I19" t="str">
-        <v>Anh: 2.8 (Tổng: 28.3)</v>
-      </c>
-      <c r="J19" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K19" t="str">
-        <v>Chỉ cam kết theo dõi tâm lý lứa tuổi, không khảo sát văn hóa</v>
+        <v>Dưới TB</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>16</v>
+      <c r="A20" t="str">
+        <v/>
       </c>
       <c r="B20" t="str">
-        <v>CS1</v>
+        <v/>
       </c>
       <c r="C20" t="str">
-        <v>0601012303</v>
+        <v/>
       </c>
       <c r="D20" t="str">
-        <v>Nguyễn Daniil</v>
+        <v/>
       </c>
       <c r="E20" t="str">
-        <v>1.1_CS1</v>
+        <v>Tiếng Anh</v>
       </c>
       <c r="F20" t="str">
-        <v>Khối 1</v>
+        <v>1.9</v>
       </c>
       <c r="G20" t="str">
-        <v>Tiếng Việt</v>
+        <v>5.2</v>
       </c>
       <c r="H20" t="str">
-        <v>Thiếu môn CKĐV</v>
+        <v>Bứt phá (+3.3)</v>
       </c>
       <c r="I20" t="str">
-        <v>Anh: 1.3 (Tổng: 13.3)</v>
-      </c>
-      <c r="J20" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K20" t="str">
-        <v>Học sinh nước ngoài / song ngữ (chưa qua khảo sát Tiếng Việt đầu vào)</v>
+        <v>Đạt chuẩn</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Phạm Gia Hương</v>
+      </c>
+      <c r="C21" t="str">
+        <v>10.2_CS1</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Khối 10</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F21" t="str">
+        <v>3.8</v>
+      </c>
+      <c r="G21" t="str">
+        <v>5.1</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Tiến bộ (+1.3)</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v/>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F22" t="str">
+        <v>3</v>
+      </c>
+      <c r="G22" t="str">
+        <v>4</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Tăng nhẹ (+1)</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>11</v>
+      </c>
+      <c r="B23" t="str">
+        <v xml:space="preserve">Đỗ An Nhiên </v>
+      </c>
+      <c r="C23" t="str">
+        <v>1.1_CS1</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F23" t="str">
+        <v>1.0</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Chưa thi (Khối 1)</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Chưa KSĐN (Khối 1)</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>12</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Hà Đặng Phước Huy</v>
+      </c>
+      <c r="C24" t="str">
+        <v>1S_CS4</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F24" t="str">
+        <v>3.3</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Chưa thi (Khối 1)</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Chưa KSĐN (Khối 1)</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>13</v>
+      </c>
+      <c r="B25" t="str">
+        <v xml:space="preserve">Trần Hoàng Anh </v>
+      </c>
+      <c r="C25" t="str">
+        <v>9.2_CS1</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Khối 9</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F25" t="str">
+        <v>2.0</v>
+      </c>
+      <c r="G25" t="str">
+        <v>4</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Tăng nhẹ (+2)</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v/>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F26" t="str">
+        <v>4</v>
+      </c>
+      <c r="G26" t="str">
+        <v>6.5</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Tiến bộ (+2.5)</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>14</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Nguyễn Ngọc Thiên Bảo</v>
+      </c>
+      <c r="C27" t="str">
+        <v>2.3INT_CS1</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Khối 2</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F27" t="str">
+        <v>3.9</v>
+      </c>
+      <c r="G27" t="str">
+        <v>4</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Chưa tiến bộ (+0.1)</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>15</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Nguyễn Thanh Thảo</v>
+      </c>
+      <c r="C28" t="str">
+        <v>9.4_CS1</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Khối 9</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Chưa có điểm</v>
+      </c>
+      <c r="G28" t="str">
+        <v>4.6</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Chưa có KSĐV</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>16</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Lê Khánh Hà</v>
+      </c>
+      <c r="C29" t="str">
+        <v>10.2_CS1</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Khối 10</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F29" t="str">
+        <v>4</v>
+      </c>
+      <c r="G29" t="str">
+        <v>7</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Bứt phá (+3)</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v/>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F30" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="G30" t="str">
+        <v>4</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Tăng nhẹ (+2.8)</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
         <v>17</v>
       </c>
-      <c r="B21" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C21" t="str">
-        <v>0601012153</v>
-      </c>
-      <c r="D21" t="str">
+      <c r="B31" t="str">
+        <v xml:space="preserve">Nguyễn Đại Phúc </v>
+      </c>
+      <c r="C31" t="str">
+        <v>10.1_CS1</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Khối 10</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F31" t="str">
+        <v>4.4</v>
+      </c>
+      <c r="G31" t="str">
+        <v>6.2</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Tiến bộ (+1.8)</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>18</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Lê Đình Sĩ Phú</v>
+      </c>
+      <c r="C32" t="str">
+        <v>6.1_CS1</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Khối 6</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F32" t="str">
+        <v>4</v>
+      </c>
+      <c r="G32" t="str">
+        <v>6</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Tiến bộ (+2)</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>19</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Ngô Thục Đan</v>
+      </c>
+      <c r="C33" t="str">
+        <v>9.1_CS1</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Khối 9</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Tâm lý</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Theo dõi tâm lý</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Toán: 3; Văn: 8.5; Anh: 7.5</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Theo dõi tốt</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>20</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Lê Nguyệt Cát</v>
+      </c>
+      <c r="C34" t="str">
+        <v>7.4_CS1</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Khối 7</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F34" t="str">
+        <v>2.6</v>
+      </c>
+      <c r="G34" t="str">
+        <v>3.7</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Tăng nhẹ (+1.1)</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>21</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Hoàng Bảo Quyên</v>
+      </c>
+      <c r="C35" t="str">
+        <v>9.2_CS1</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Khối 9</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F35" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="G35" t="str">
+        <v>4.6</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Tăng nhẹ (+2.4)</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>22</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Phạm Gia Bảo</v>
+      </c>
+      <c r="C36" t="str">
+        <v>9.3_CS1</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Khối 9</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F36" t="str">
+        <v>1.0</v>
+      </c>
+      <c r="G36" t="str">
+        <v>3.6</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Tăng nhẹ (+2.6)</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v/>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F37" t="str">
+        <v>4</v>
+      </c>
+      <c r="G37" t="str">
+        <v>3.75</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Chưa tiến bộ</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>23</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Đặng Hoàng Như Ý</v>
+      </c>
+      <c r="C38" t="str">
+        <v>10.2_CS1</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Khối 10</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F38" t="str">
+        <v>4.6</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Chưa thi</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Chưa thi KSĐN</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Chưa có bài KSĐN</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>24</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Phạm Hải Như</v>
+      </c>
+      <c r="C39" t="str">
+        <v>10.2_CS1</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Khối 10</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F39" t="str">
+        <v>4.6</v>
+      </c>
+      <c r="G39" t="str">
+        <v>4.6</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Chưa tiến bộ</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>25</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Nguyễn Thành Long</v>
+      </c>
+      <c r="C40" t="str">
+        <v>7.3_CS1</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Khối 9</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F40" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G40" t="str">
+        <v>6</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Bứt phá (+3.2)</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>26</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Trần Quang Thiên Ân</v>
+      </c>
+      <c r="C41" t="str">
+        <v>10.1_CS1</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Khối 10</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F41" t="str">
+        <v>3</v>
+      </c>
+      <c r="G41" t="str">
+        <v>7.25</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Bứt phá (+4.3)</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>27</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Lê Hồ Gia Huy</v>
+      </c>
+      <c r="C42" t="str">
+        <v>10.2_CS1</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Khối 10</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F42" t="str">
+        <v>2.7</v>
+      </c>
+      <c r="G42" t="str">
+        <v>4.4</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Tăng nhẹ (+1.7)</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>28</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Trương Lê Hưng Phát</v>
+      </c>
+      <c r="C43" t="str">
+        <v>12.1_CS1</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Khối 12</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F43" t="str">
+        <v>4</v>
+      </c>
+      <c r="G43" t="str">
+        <v>5.1</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Tiến bộ (+1.1)</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>29</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Nguyễn Văn Tuấn Kiệt</v>
+      </c>
+      <c r="C44" t="str">
+        <v>9.2_CS1</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Khối 9</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F44" t="str">
+        <v>5</v>
+      </c>
+      <c r="G44" t="str">
+        <v>3</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Chưa tiến bộ</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v/>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F45" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="G45" t="str">
+        <v>2.9</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Chưa tiến bộ</v>
+      </c>
+      <c r="I45" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>30</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Nguyễn Daniil</v>
+      </c>
+      <c r="C46" t="str">
+        <v>1.1_CS1</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Tiếng Việt</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Chưa có điểm</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Chưa thi (Khối 1)</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="I46" t="str">
+        <v>Chưa KSĐN (Khối 1)</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>31</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Trần Đăng Quang</v>
+      </c>
+      <c r="C47" t="str">
+        <v>6.3_CS1</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Khối 6</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F47" t="str">
+        <v>4.3</v>
+      </c>
+      <c r="G47" t="str">
+        <v>5.6</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Tiến bộ (+1.3)</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>32</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Trần Thục Quyên</v>
+      </c>
+      <c r="C48" t="str">
+        <v>7.4_CS1</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Khối 7</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F48" t="str">
+        <v>4.3</v>
+      </c>
+      <c r="G48" t="str">
+        <v>6</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Tiến bộ (+1.7)</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>33</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Lương Bích Ngọc</v>
+      </c>
+      <c r="C49" t="str">
+        <v>6.3_CS1</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Khối 6</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F49" t="str">
+        <v>4.3</v>
+      </c>
+      <c r="G49" t="str">
+        <v>5</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Tiến bộ (+0.7)</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>34</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Nguyễn Quỳnh Như</v>
+      </c>
+      <c r="C50" t="str">
+        <v>3.1_CS1</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Khối 6</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F50" t="str">
+        <v>3.9</v>
+      </c>
+      <c r="G50" t="str">
+        <v>9.1</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Bứt phá (+5.2)</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>35</v>
+      </c>
+      <c r="B51" t="str">
         <v>Nguyễn Ngọc Minh</v>
       </c>
-      <c r="E21" t="str">
+      <c r="C51" t="str">
         <v>7.2_CS1</v>
       </c>
-      <c r="F21" t="str">
+      <c r="D51" t="str">
         <v>Khối 7</v>
       </c>
-      <c r="G21" t="str">
+      <c r="E51" t="str">
         <v>Tiếng Anh</v>
       </c>
-      <c r="H21" t="str">
-        <v>Thiếu môn CKĐV</v>
-      </c>
-      <c r="I21" t="str">
-        <v>Toán: 6; Ngữ Văn: 7</v>
-      </c>
-      <c r="J21" t="str">
-        <v>Toán: 8.75; Ngữ Văn: 5.75; Anh: 4.1</v>
-      </c>
-      <c r="K21" t="str">
-        <v>Môn Tiếng Anh chưa nhập điểm trên hệ thống (đã có điểm Toán, Văn)</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>18</v>
-      </c>
-      <c r="B22" t="str">
-        <v>CS2</v>
-      </c>
-      <c r="C22" t="str">
-        <v>0701020109</v>
-      </c>
-      <c r="D22" t="str">
+      <c r="F51" t="str">
+        <v>2.3</v>
+      </c>
+      <c r="G51" t="str">
+        <v>8.9</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Bứt phá (+6.6)</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>36</v>
+      </c>
+      <c r="B52" t="str">
+        <v xml:space="preserve">Nguyễn Đặng Bảo Trâm </v>
+      </c>
+      <c r="C52" t="str">
+        <v>8.2_CS1</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Khối 8</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Chung / Theo dõi</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Theo dõi chung</v>
+      </c>
+      <c r="G52" t="str">
+        <v>—</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Chưa thi KSĐN</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Chưa có bài KSĐN</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>HS Cam kết theo môn:</v>
+      </c>
+      <c r="B53" t="str">
+        <v/>
+      </c>
+      <c r="C53" t="str">
+        <v/>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v>Tiếng Anh: 29 HS | Toán: 12 HS | Tiếng Việt: 1 HS | Ngữ Văn: 1 HS | Tâm lý: 1 HS | Khác: 1 HS</v>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Tổng số môn Tiến bộ:</v>
+      </c>
+      <c r="B54" t="str">
+        <v/>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v>19 / 38 lượt môn (50.0%)</v>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Tổng số môn Đạt chuẩn:</v>
+      </c>
+      <c r="B55" t="str">
+        <v/>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v>19 / 38 lượt môn (50.0%) (Đạt chuẩn: 19, TB: 0, Dưới TB: 19)</v>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>&gt;&gt;&gt; CƠ SỞ: CS2 (8 HỌC SINH CKĐV)</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>STT</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Họ và tên</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Lớp</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Khối</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Môn CKĐV</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Điểm KSĐV</v>
+      </c>
+      <c r="G58" t="str">
+        <v>Điểm KSĐN</v>
+      </c>
+      <c r="H58" t="str">
+        <v>Tiến bộ</v>
+      </c>
+      <c r="I58" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>1</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Lê Gia Lân</v>
+      </c>
+      <c r="C59" t="str">
+        <v>1.3_CS2</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Tâm lý</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Theo dõi tâm lý</v>
+      </c>
+      <c r="G59" t="str">
+        <v>Chưa có bài KSĐN (Khối 1)</v>
+      </c>
+      <c r="H59" t="str">
+        <v>Theo dõi tâm lý</v>
+      </c>
+      <c r="I59" t="str">
+        <v>Theo dõi tâm lý</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>2</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Đào Trần Thảo Linh</v>
+      </c>
+      <c r="C60" t="str">
+        <v>1.3_CS2</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Tâm lý</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Theo dõi tâm lý</v>
+      </c>
+      <c r="G60" t="str">
+        <v>Chưa có bài KSĐN (Khối 1)</v>
+      </c>
+      <c r="H60" t="str">
+        <v>Theo dõi tâm lý</v>
+      </c>
+      <c r="I60" t="str">
+        <v>Theo dõi tâm lý</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v/>
+      </c>
+      <c r="B61" t="str">
+        <v/>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v>Tiếng Việt</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Chưa có điểm</v>
+      </c>
+      <c r="G61" t="str">
+        <v>Chưa thi (Khối 1)</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Chưa KSĐN (Khối 1)</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>3</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Nguyễn Thanh Phúc</v>
+      </c>
+      <c r="C62" t="str">
+        <v>1.2INT_CS2</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F62" t="str">
+        <v>1.7</v>
+      </c>
+      <c r="G62" t="str">
+        <v>Chưa thi (Khối 1)</v>
+      </c>
+      <c r="H62" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="I62" t="str">
+        <v>Chưa KSĐN (Khối 1)</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>4</v>
+      </c>
+      <c r="B63" t="str">
+        <v>ĐỖ NGUYỄN AN KHÔI</v>
+      </c>
+      <c r="C63" t="str">
+        <v>1.3_CS2</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Chung / Theo dõi</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Theo dõi chung</v>
+      </c>
+      <c r="G63" t="str">
+        <v>—</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Chưa KSĐN (Khối 1)</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Phan Hải Đăng</v>
+      </c>
+      <c r="C64" t="str">
+        <v>1.3_CS2</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Chung / Theo dõi</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Theo dõi chung</v>
+      </c>
+      <c r="G64" t="str">
+        <v>—</v>
+      </c>
+      <c r="H64" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="I64" t="str">
+        <v>Chưa KSĐN (Khối 1)</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>6</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Hoàng Bữu Minh Hưng</v>
+      </c>
+      <c r="C65" t="str">
+        <v>3.4_CS2</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Khối 3</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F65" t="str">
+        <v>4.2</v>
+      </c>
+      <c r="G65" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Tiến bộ (+1.3)</v>
+      </c>
+      <c r="I65" t="str">
+        <v>Trung bình</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>7</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Lê Hồ Duy Khang</v>
+      </c>
+      <c r="C66" t="str">
+        <v>1.3_CS2</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Tâm lý</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Theo dõi tâm lý</v>
+      </c>
+      <c r="G66" t="str">
+        <v>Chưa có bài KSĐN (Khối 1)</v>
+      </c>
+      <c r="H66" t="str">
+        <v>Theo dõi tâm lý</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Theo dõi tâm lý</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>8</v>
+      </c>
+      <c r="B67" t="str">
         <v>Sangadziev Aron</v>
       </c>
-      <c r="E22" t="str">
+      <c r="C67" t="str">
         <v>1.2INT_CS2</v>
       </c>
-      <c r="F22" t="str">
+      <c r="D67" t="str">
         <v>Khối 1</v>
       </c>
-      <c r="G22" t="str">
+      <c r="E67" t="str">
         <v>Tiếng Việt</v>
       </c>
-      <c r="H22" t="str">
-        <v>Thiếu môn CKĐV</v>
-      </c>
-      <c r="I22" t="str">
-        <v>Anh: 2.7 (Tổng: 26.7)</v>
-      </c>
-      <c r="J22" t="str">
+      <c r="F67" t="str">
+        <v>Chưa có điểm</v>
+      </c>
+      <c r="G67" t="str">
+        <v>Chưa thi (Khối 1)</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="I67" t="str">
+        <v>Chưa KSĐN (Khối 1)</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>HS Cam kết theo môn:</v>
+      </c>
+      <c r="B68" t="str">
+        <v/>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v>Tiếng Anh: 2 HS | Tiếng Việt: 2 HS | Tâm lý: 3 HS | Khác: 2 HS</v>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Tổng số môn Tiến bộ:</v>
+      </c>
+      <c r="B69" t="str">
+        <v/>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v>1 / 1 lượt môn (100.0%)</v>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Tổng số môn Đạt chuẩn:</v>
+      </c>
+      <c r="B70" t="str">
+        <v/>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v>0 / 1 lượt môn (0.0%) (Đạt chuẩn: 0, TB: 1, Dưới TB: 0)</v>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>&gt;&gt;&gt; CƠ SỞ: CS3 (8 HỌC SINH CKĐV)</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>STT</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Họ và tên</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Lớp</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Khối</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Môn CKĐV</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Điểm KSĐV</v>
+      </c>
+      <c r="G73" t="str">
+        <v>Điểm KSĐN</v>
+      </c>
+      <c r="H73" t="str">
+        <v>Tiến bộ</v>
+      </c>
+      <c r="I73" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>1</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Phan Anh Quân</v>
+      </c>
+      <c r="C74" t="str">
+        <v>9INT_CS3</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Khối 9</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Chưa có điểm</v>
+      </c>
+      <c r="G74" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="H74" t="str">
+        <v>Chưa có KSĐV</v>
+      </c>
+      <c r="I74" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v/>
+      </c>
+      <c r="B75" t="str">
+        <v/>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F75" t="str">
+        <v>4.1</v>
+      </c>
+      <c r="G75" t="str">
+        <v>5.6</v>
+      </c>
+      <c r="H75" t="str">
+        <v>Tiến bộ (+1.5)</v>
+      </c>
+      <c r="I75" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>2</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Đoàn Ngọc Thảo Chloe</v>
+      </c>
+      <c r="C76" t="str">
+        <v>2.1INT_CS3</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Khối 2</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Tiếng Việt</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Chưa có điểm</v>
+      </c>
+      <c r="G76" t="str">
+        <v>4</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Chưa có KSĐV</v>
+      </c>
+      <c r="I76" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v/>
+      </c>
+      <c r="B77" t="str">
+        <v/>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F77" t="str">
+        <v>8.4</v>
+      </c>
+      <c r="G77" t="str">
+        <v>9.8</v>
+      </c>
+      <c r="H77" t="str">
+        <v>Tiến bộ (+1.4)</v>
+      </c>
+      <c r="I77" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>3</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Hồ Hữu Bách</v>
+      </c>
+      <c r="C78" t="str">
+        <v>4UK_CS3</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Khối 4</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Tiếng Việt</v>
+      </c>
+      <c r="F78" t="str">
+        <v>3</v>
+      </c>
+      <c r="G78" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="H78" t="str">
+        <v>Chưa tiến bộ</v>
+      </c>
+      <c r="I78" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>4</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Govorushko Mikhail</v>
+      </c>
+      <c r="C79" t="str">
+        <v>1.1INT_CS3</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Tiếng Việt</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Chưa có điểm</v>
+      </c>
+      <c r="G79" t="str">
+        <v>Chưa thi (Khối 1)</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="I79" t="str">
+        <v>Chưa KSĐN (Khối 1)</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>5</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Lecomte Mailys Mộc Yên</v>
+      </c>
+      <c r="C80" t="str">
+        <v>4INT_CS3</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Khối 4</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Tiếng Việt</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Chưa có điểm</v>
+      </c>
+      <c r="G80" t="str">
+        <v>5</v>
+      </c>
+      <c r="H80" t="str">
+        <v>Chưa có KSĐV</v>
+      </c>
+      <c r="I80" t="str">
+        <v>Trung bình</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v/>
+      </c>
+      <c r="B81" t="str">
+        <v/>
+      </c>
+      <c r="C81" t="str">
+        <v/>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F81" t="str">
+        <v>9.6</v>
+      </c>
+      <c r="G81" t="str">
+        <v>7.3</v>
+      </c>
+      <c r="H81" t="str">
+        <v>Không tăng (-2.3)</v>
+      </c>
+      <c r="I81" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>6</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Hà Minh Khuê</v>
+      </c>
+      <c r="C82" t="str">
+        <v>5.1INT_CS3</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Khối 5</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F82" t="str">
+        <v>4.6</v>
+      </c>
+      <c r="G82" t="str">
+        <v>3.6</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Chưa tiến bộ</v>
+      </c>
+      <c r="I82" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>7</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Phùng Đức Thiên Ân</v>
+      </c>
+      <c r="C83" t="str">
+        <v>3.1INT_CS3</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Khối 3</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F83" t="str">
+        <v>3.6</v>
+      </c>
+      <c r="G83" t="str">
+        <v>6.55</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Tiến bộ (+2.9)</v>
+      </c>
+      <c r="I83" t="str">
+        <v>Trung bình</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>8</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Phùng Chí Nam Anh</v>
+      </c>
+      <c r="C84" t="str">
+        <v>8.1INT_CS3</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Khối 8</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F84" t="str">
+        <v>3.0</v>
+      </c>
+      <c r="G84" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="H84" t="str">
+        <v>Tăng nhẹ (+0.5)</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>HS Cam kết theo môn:</v>
+      </c>
+      <c r="B85" t="str">
+        <v/>
+      </c>
+      <c r="C85" t="str">
+        <v/>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v>Tiếng Anh: 6 HS | Toán: 1 HS | Tiếng Việt: 4 HS</v>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Tổng số môn Tiến bộ:</v>
+      </c>
+      <c r="B86" t="str">
+        <v/>
+      </c>
+      <c r="C86" t="str">
+        <v/>
+      </c>
+      <c r="D86" t="str">
+        <v/>
+      </c>
+      <c r="E86" t="str">
+        <v>3 / 7 lượt môn (42.9%)</v>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Tổng số môn Đạt chuẩn:</v>
+      </c>
+      <c r="B87" t="str">
+        <v/>
+      </c>
+      <c r="C87" t="str">
+        <v/>
+      </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
+      <c r="E87" t="str">
+        <v>3 / 7 lượt môn (42.9%) (Đạt chuẩn: 3, TB: 1, Dưới TB: 3)</v>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>&gt;&gt;&gt; CƠ SỞ: CS4 (12 HỌC SINH CKĐV)</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>STT</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Họ và tên</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Lớp</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Khối</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Môn CKĐV</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Điểm KSĐV</v>
+      </c>
+      <c r="G90" t="str">
+        <v>Điểm KSĐN</v>
+      </c>
+      <c r="H90" t="str">
+        <v>Tiến bộ</v>
+      </c>
+      <c r="I90" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>1</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Ayesha Mirza</v>
+      </c>
+      <c r="C91" t="str">
+        <v>6S_CS4</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Khối 6</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F91" t="str">
+        <v>4</v>
+      </c>
+      <c r="G91" t="str">
+        <v>3.8</v>
+      </c>
+      <c r="H91" t="str">
+        <v>Chưa tiến bộ</v>
+      </c>
+      <c r="I91" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v/>
+      </c>
+      <c r="B92" t="str">
+        <v/>
+      </c>
+      <c r="C92" t="str">
+        <v/>
+      </c>
+      <c r="D92" t="str">
+        <v/>
+      </c>
+      <c r="E92" t="str">
+        <v>Tiếng Việt</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Chưa có điểm</v>
+      </c>
+      <c r="G92" t="str">
+        <v>Chưa thi</v>
+      </c>
+      <c r="H92" t="str">
+        <v>Chưa thi KSĐN</v>
+      </c>
+      <c r="I92" t="str">
         <v>Chưa có bài KSĐN</v>
       </c>
-      <c r="K22" t="str">
-        <v>Học sinh nước ngoài / song ngữ (chưa qua khảo sát Tiếng Việt đầu vào)</v>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>2</v>
+      </c>
+      <c r="B93" t="str">
+        <v>HÀ ĐẶNG BẢO NGỌC</v>
+      </c>
+      <c r="C93" t="str">
+        <v>3S_CS4</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Khối 3</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F93" t="str">
+        <v>4.0</v>
+      </c>
+      <c r="G93" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Chưa tiến bộ</v>
+      </c>
+      <c r="I93" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>3</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Nguyễn Thị Thu Thúy</v>
+      </c>
+      <c r="C94" t="str">
+        <v>10S_CS4</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Khối 10</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F94" t="str">
+        <v>1.8</v>
+      </c>
+      <c r="G94" t="str">
+        <v>1.9</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Tăng nhẹ (+0.1)</v>
+      </c>
+      <c r="I94" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>4</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Huỳnh Hoàng An</v>
+      </c>
+      <c r="C95" t="str">
+        <v>3S_CS4</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Khối 3</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F95" t="str">
+        <v>5</v>
+      </c>
+      <c r="G95" t="str">
+        <v>8.3</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Bứt phá (+3.3)</v>
+      </c>
+      <c r="I95" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v/>
+      </c>
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
+        <v/>
+      </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <v>Tiếng Việt</v>
+      </c>
+      <c r="F96" t="str">
+        <v>4.5</v>
+      </c>
+      <c r="G96" t="str">
+        <v>3</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Chưa tiến bộ</v>
+      </c>
+      <c r="I96" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v/>
+      </c>
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
+        <v/>
+      </c>
+      <c r="D97" t="str">
+        <v/>
+      </c>
+      <c r="E97" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F97" t="str">
+        <v>8.7</v>
+      </c>
+      <c r="G97" t="str">
+        <v>9.8</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Tiến bộ (+1.1)</v>
+      </c>
+      <c r="I97" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>5</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Đặng Ngọc Bảo Ngân</v>
+      </c>
+      <c r="C98" t="str">
+        <v>10S_CS4</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Khối 10</v>
+      </c>
+      <c r="E98" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F98" t="str">
+        <v>1.8</v>
+      </c>
+      <c r="G98" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Tăng nhẹ (+0.7)</v>
+      </c>
+      <c r="I98" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>6</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Ngô Nhật Khang</v>
+      </c>
+      <c r="C99" t="str">
+        <v>10S_CS4</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Khối 10</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F99" t="str">
+        <v>1.8</v>
+      </c>
+      <c r="G99" t="str">
+        <v>3.1</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Tăng nhẹ (+1.3)</v>
+      </c>
+      <c r="I99" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v/>
+      </c>
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
+        <v/>
+      </c>
+      <c r="D100" t="str">
+        <v/>
+      </c>
+      <c r="E100" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F100" t="str">
+        <v>4</v>
+      </c>
+      <c r="G100" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Chưa tiến bộ</v>
+      </c>
+      <c r="I100" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v/>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v/>
+      </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v>Ngữ Văn</v>
+      </c>
+      <c r="F101" t="str">
+        <v>4.5</v>
+      </c>
+      <c r="G101" t="str">
+        <v>5.75</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Tiến bộ (+1.3)</v>
+      </c>
+      <c r="I101" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>7</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Võ Hoàng Vi</v>
+      </c>
+      <c r="C102" t="str">
+        <v>6S_CS4</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Khối 6</v>
+      </c>
+      <c r="E102" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F102" t="str">
+        <v>3</v>
+      </c>
+      <c r="G102" t="str">
+        <v>6</v>
+      </c>
+      <c r="H102" t="str">
+        <v>Bứt phá (+3)</v>
+      </c>
+      <c r="I102" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>8</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Võ Như Quỳnh</v>
+      </c>
+      <c r="C103" t="str">
+        <v>7S_CS4</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Khối 7</v>
+      </c>
+      <c r="E103" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F103" t="str">
+        <v>4.5</v>
+      </c>
+      <c r="G103" t="str">
+        <v>6</v>
+      </c>
+      <c r="H103" t="str">
+        <v>Tiến bộ (+1.5)</v>
+      </c>
+      <c r="I103" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v/>
+      </c>
+      <c r="B104" t="str">
+        <v/>
+      </c>
+      <c r="C104" t="str">
+        <v/>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v>Ngữ Văn</v>
+      </c>
+      <c r="F104" t="str">
+        <v>5</v>
+      </c>
+      <c r="G104" t="str">
+        <v>6</v>
+      </c>
+      <c r="H104" t="str">
+        <v>Tiến bộ (+1)</v>
+      </c>
+      <c r="I104" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v/>
+      </c>
+      <c r="B105" t="str">
+        <v/>
+      </c>
+      <c r="C105" t="str">
+        <v/>
+      </c>
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F105" t="str">
+        <v>4.2</v>
+      </c>
+      <c r="G105" t="str">
+        <v>2.9</v>
+      </c>
+      <c r="H105" t="str">
+        <v>Chưa tiến bộ</v>
+      </c>
+      <c r="I105" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>9</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Đỗ Thành Nguyên</v>
+      </c>
+      <c r="C106" t="str">
+        <v>10S_CS4</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Khối 10</v>
+      </c>
+      <c r="E106" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F106" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="G106" t="str">
+        <v>0</v>
+      </c>
+      <c r="H106" t="str">
+        <v>Chưa tiến bộ</v>
+      </c>
+      <c r="I106" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v/>
+      </c>
+      <c r="B107" t="str">
+        <v/>
+      </c>
+      <c r="C107" t="str">
+        <v/>
+      </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v>Ngữ Văn</v>
+      </c>
+      <c r="F107" t="str">
+        <v>5</v>
+      </c>
+      <c r="G107" t="str">
+        <v>Chưa thi</v>
+      </c>
+      <c r="H107" t="str">
+        <v>Chưa thi KSĐN</v>
+      </c>
+      <c r="I107" t="str">
+        <v>Chưa có bài KSĐN</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v/>
+      </c>
+      <c r="B108" t="str">
+        <v/>
+      </c>
+      <c r="C108" t="str">
+        <v/>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F108" t="str">
+        <v>1.0</v>
+      </c>
+      <c r="G108" t="str">
+        <v>Chưa thi</v>
+      </c>
+      <c r="H108" t="str">
+        <v>Chưa thi KSĐN</v>
+      </c>
+      <c r="I108" t="str">
+        <v>Chưa có bài KSĐN</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>10</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Phạm Kiều Anh</v>
+      </c>
+      <c r="C109" t="str">
+        <v>6S_CS4</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Khối 6</v>
+      </c>
+      <c r="E109" t="str">
+        <v>Ngữ Văn</v>
+      </c>
+      <c r="F109" t="str">
+        <v>4</v>
+      </c>
+      <c r="G109" t="str">
+        <v>7</v>
+      </c>
+      <c r="H109" t="str">
+        <v>Bứt phá (+3)</v>
+      </c>
+      <c r="I109" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>11</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Võ Thị Anh Thư</v>
+      </c>
+      <c r="C110" t="str">
+        <v>7S_CS4</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Khối 7</v>
+      </c>
+      <c r="E110" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F110" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="G110" t="str">
+        <v>2.6</v>
+      </c>
+      <c r="H110" t="str">
+        <v>Tăng nhẹ (+0.1)</v>
+      </c>
+      <c r="I110" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>12</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Ngô Huỳnh Anh Minh</v>
+      </c>
+      <c r="C111" t="str">
+        <v>6S_CS4</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Khối 6</v>
+      </c>
+      <c r="E111" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F111" t="str">
+        <v>4</v>
+      </c>
+      <c r="G111" t="str">
+        <v>Chưa thi</v>
+      </c>
+      <c r="H111" t="str">
+        <v>Chưa thi KSĐN</v>
+      </c>
+      <c r="I111" t="str">
+        <v>Chưa có bài KSĐN</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v/>
+      </c>
+      <c r="B112" t="str">
+        <v/>
+      </c>
+      <c r="C112" t="str">
+        <v/>
+      </c>
+      <c r="D112" t="str">
+        <v/>
+      </c>
+      <c r="E112" t="str">
+        <v>Ngữ Văn</v>
+      </c>
+      <c r="F112" t="str">
+        <v>5</v>
+      </c>
+      <c r="G112" t="str">
+        <v>Chưa thi</v>
+      </c>
+      <c r="H112" t="str">
+        <v>Chưa thi KSĐN</v>
+      </c>
+      <c r="I112" t="str">
+        <v>Chưa có bài KSĐN</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>HS Cam kết theo môn:</v>
+      </c>
+      <c r="B113" t="str">
+        <v/>
+      </c>
+      <c r="C113" t="str">
+        <v/>
+      </c>
+      <c r="D113" t="str">
+        <v/>
+      </c>
+      <c r="E113" t="str">
+        <v>Tiếng Anh: 8 HS | Toán: 7 HS | Tiếng Việt: 2 HS | Ngữ Văn: 5 HS</v>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Tổng số môn Tiến bộ:</v>
+      </c>
+      <c r="B114" t="str">
+        <v/>
+      </c>
+      <c r="C114" t="str">
+        <v/>
+      </c>
+      <c r="D114" t="str">
+        <v/>
+      </c>
+      <c r="E114" t="str">
+        <v>7 / 17 lượt môn (41.2%)</v>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Tổng số môn Đạt chuẩn:</v>
+      </c>
+      <c r="B115" t="str">
+        <v/>
+      </c>
+      <c r="C115" t="str">
+        <v/>
+      </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
+      <c r="E115" t="str">
+        <v>7 / 17 lượt môn (41.2%) (Đạt chuẩn: 7, TB: 0, Dưới TB: 10)</v>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>&gt;&gt;&gt; CƠ SỞ: CS5 (12 HỌC SINH CKĐV)</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>STT</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Họ và tên</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Lớp</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Khối</v>
+      </c>
+      <c r="E118" t="str">
+        <v>Môn CKĐV</v>
+      </c>
+      <c r="F118" t="str">
+        <v>Điểm KSĐV</v>
+      </c>
+      <c r="G118" t="str">
+        <v>Điểm KSĐN</v>
+      </c>
+      <c r="H118" t="str">
+        <v>Tiến bộ</v>
+      </c>
+      <c r="I118" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>1</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Mai Minh Minh</v>
+      </c>
+      <c r="C119" t="str">
+        <v>6.5_CS5</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Khối 6</v>
+      </c>
+      <c r="E119" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F119" t="str">
+        <v>3.4</v>
+      </c>
+      <c r="G119" t="str">
+        <v>4.5</v>
+      </c>
+      <c r="H119" t="str">
+        <v>Tăng nhẹ (+1.1)</v>
+      </c>
+      <c r="I119" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>2</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Lâm Minh Khang</v>
+      </c>
+      <c r="C120" t="str">
+        <v>2.5_CS5</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Khối 2</v>
+      </c>
+      <c r="E120" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F120" t="str">
+        <v>6.1</v>
+      </c>
+      <c r="G120" t="str">
+        <v>6.1</v>
+      </c>
+      <c r="H120" t="str">
+        <v>Không tăng (0)</v>
+      </c>
+      <c r="I120" t="str">
+        <v>Trung bình</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>3</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Đặng Ái Thiên Vân</v>
+      </c>
+      <c r="C121" t="str">
+        <v>3.6_CS5</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Khối 3</v>
+      </c>
+      <c r="E121" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F121" t="str">
+        <v>3.9</v>
+      </c>
+      <c r="G121" t="str">
+        <v>5.6</v>
+      </c>
+      <c r="H121" t="str">
+        <v>Tiến bộ (+1.7)</v>
+      </c>
+      <c r="I121" t="str">
+        <v>Trung bình</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>4</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Bùi Tuấn Anh</v>
+      </c>
+      <c r="C122" t="str">
+        <v>7.5_CS5</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Khối 7</v>
+      </c>
+      <c r="E122" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F122" t="str">
+        <v>2.0</v>
+      </c>
+      <c r="G122" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="H122" t="str">
+        <v>Tăng nhẹ (+1.5)</v>
+      </c>
+      <c r="I122" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>5</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Phạm Gia Hưng</v>
+      </c>
+      <c r="C123" t="str">
+        <v>2.5_CS5</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Khối 7</v>
+      </c>
+      <c r="E123" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F123" t="str">
+        <v>2.6</v>
+      </c>
+      <c r="G123" t="str">
+        <v>6.8</v>
+      </c>
+      <c r="H123" t="str">
+        <v>Bứt phá (+4.2)</v>
+      </c>
+      <c r="I123" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>6</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Vũ Đức Thịnh</v>
+      </c>
+      <c r="C124" t="str">
+        <v>1.5_CS5</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="E124" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F124" t="str">
+        <v>1.0</v>
+      </c>
+      <c r="G124" t="str">
+        <v>Chưa thi (Khối 1)</v>
+      </c>
+      <c r="H124" t="str">
+        <v>Khối 1</v>
+      </c>
+      <c r="I124" t="str">
+        <v>Chưa KSĐN (Khối 1)</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>7</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Nguyễn Minh Anh</v>
+      </c>
+      <c r="C125" t="str">
+        <v>6.5_CS5</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Khối 6</v>
+      </c>
+      <c r="E125" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F125" t="str">
+        <v>3.0</v>
+      </c>
+      <c r="G125" t="str">
+        <v>9.2</v>
+      </c>
+      <c r="H125" t="str">
+        <v>Bứt phá (+6.2)</v>
+      </c>
+      <c r="I125" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>8</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Đỗ Duy Khôi</v>
+      </c>
+      <c r="C126" t="str">
+        <v>6.5_CS5</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Khối 6</v>
+      </c>
+      <c r="E126" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F126" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="G126" t="str">
+        <v>4.5</v>
+      </c>
+      <c r="H126" t="str">
+        <v>Chưa tiến bộ</v>
+      </c>
+      <c r="I126" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v/>
+      </c>
+      <c r="B127" t="str">
+        <v/>
+      </c>
+      <c r="C127" t="str">
+        <v/>
+      </c>
+      <c r="D127" t="str">
+        <v/>
+      </c>
+      <c r="E127" t="str">
+        <v>Toán</v>
+      </c>
+      <c r="F127" t="str">
+        <v>4</v>
+      </c>
+      <c r="G127" t="str">
+        <v>2.25</v>
+      </c>
+      <c r="H127" t="str">
+        <v>Chưa tiến bộ</v>
+      </c>
+      <c r="I127" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>9</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Lê Nguyễn Hoàng Bảo</v>
+      </c>
+      <c r="C128" t="str">
+        <v>7.5_CS5</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Khối 7</v>
+      </c>
+      <c r="E128" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F128" t="str">
+        <v>1.7</v>
+      </c>
+      <c r="G128" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H128" t="str">
+        <v>Tăng nhẹ (+1.5)</v>
+      </c>
+      <c r="I128" t="str">
+        <v>Dưới TB</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>10</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Nguyễn Hoàng Đạt</v>
+      </c>
+      <c r="C129" t="str">
+        <v>3.2INT_CS5</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Khối 3</v>
+      </c>
+      <c r="E129" t="str">
+        <v>Chung / Theo dõi</v>
+      </c>
+      <c r="F129" t="str">
+        <v>Theo dõi chung</v>
+      </c>
+      <c r="G129" t="str">
+        <v>—</v>
+      </c>
+      <c r="H129" t="str">
+        <v>Chưa thi KSĐN</v>
+      </c>
+      <c r="I129" t="str">
+        <v>Chưa có bài KSĐN</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>11</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Nguyễn Hoàng Phúc</v>
+      </c>
+      <c r="C130" t="str">
+        <v>5.2INT_CS5</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Khối 5</v>
+      </c>
+      <c r="E130" t="str">
+        <v>Chung / Theo dõi</v>
+      </c>
+      <c r="F130" t="str">
+        <v>Theo dõi chung</v>
+      </c>
+      <c r="G130" t="str">
+        <v>—</v>
+      </c>
+      <c r="H130" t="str">
+        <v>Chưa thi KSĐN</v>
+      </c>
+      <c r="I130" t="str">
+        <v>Chưa có bài KSĐN</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>12</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Trần Minh Huy</v>
+      </c>
+      <c r="C131" t="str">
+        <v>2.6_CS5</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Khối 2</v>
+      </c>
+      <c r="E131" t="str">
+        <v>Tiếng Anh</v>
+      </c>
+      <c r="F131" t="str">
+        <v>7.0</v>
+      </c>
+      <c r="G131" t="str">
+        <v>8.7</v>
+      </c>
+      <c r="H131" t="str">
+        <v>Tiến bộ (+1.7)</v>
+      </c>
+      <c r="I131" t="str">
+        <v>Đạt chuẩn</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>HS Cam kết theo môn:</v>
+      </c>
+      <c r="B132" t="str">
+        <v/>
+      </c>
+      <c r="C132" t="str">
+        <v/>
+      </c>
+      <c r="D132" t="str">
+        <v/>
+      </c>
+      <c r="E132" t="str">
+        <v>Tiếng Anh: 10 HS | Toán: 1 HS | Khác: 2 HS</v>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+      <c r="H132" t="str">
+        <v/>
+      </c>
+      <c r="I132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Tổng số môn Tiến bộ:</v>
+      </c>
+      <c r="B133" t="str">
+        <v/>
+      </c>
+      <c r="C133" t="str">
+        <v/>
+      </c>
+      <c r="D133" t="str">
+        <v/>
+      </c>
+      <c r="E133" t="str">
+        <v>4 / 10 lượt môn (40.0%)</v>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133" t="str">
+        <v/>
+      </c>
+      <c r="H133" t="str">
+        <v/>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>Tổng số môn Đạt chuẩn:</v>
+      </c>
+      <c r="B134" t="str">
+        <v/>
+      </c>
+      <c r="C134" t="str">
+        <v/>
+      </c>
+      <c r="D134" t="str">
+        <v/>
+      </c>
+      <c r="E134" t="str">
+        <v>3 / 10 lượt môn (30.0%) (Đạt chuẩn: 3, TB: 2, Dưới TB: 5)</v>
+      </c>
+      <c r="F134" t="str">
+        <v/>
+      </c>
+      <c r="G134" t="str">
+        <v/>
+      </c>
+      <c r="H134" t="str">
+        <v/>
+      </c>
+      <c r="I134" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K22"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K81"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>DANH SÁCH 76 HỌC SINH CAM KẾT ĐẦU VÀO (CKĐV) ĐÃ NHẬP HỌC - MAP ĐIỂM KHẢO SÁT ĐẦU NĂM</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>* Điểm Tiếng Anh KSĐV: Lấy từ Cột Tổng điểm (Thang 100) và quy đổi chuẩn xác về Thang 10 (Scale 10 = Tổng điểm / 10)</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>* HS diện Tâm lý: Ghi chú rõ "HS Cam kết tâm lý", không hiển thị điểm thi bộ môn</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>STT</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Cơ sở</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Mã HS</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Họ và tên</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Lớp</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Khối</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Môn CKĐV</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Tình trạng KSĐV</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Điểm KSĐV Môn Cam Kết (Thang 10 &amp; Cột Tổng điểm)</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Điểm KSĐN Môn Tương Ứng</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Ghi chú &amp; Trạng thái</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C6" t="str">
-        <v>0701030312</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Nguyễn Gia Bảo</v>
-      </c>
-      <c r="E6" t="str">
-        <v>9.2_CS1</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Khối 9</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Toán, Tiếng Anh</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Toán: 4; Ngữ Văn: 6.5; Tiếng Anh: 1.0 (Tổng: 10)</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Toán: 3.5; Tiếng Việt: 8.5; Ngữ Văn: 4.25; Tiếng Anh: 8</v>
-      </c>
-      <c r="K6" t="str">
-        <v>Bứt phá ngoạn mục (+7)</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C7" t="str">
-        <v>0601011426</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Lê Nguyên Khang</v>
-      </c>
-      <c r="E7" t="str">
-        <v>2.1_CS1</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Khối 2</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Chưa có điểm KSĐV</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Chưa có điểm KSĐV (Diện Tuyển thẳng (không phải thi khảo sát đầu vào))</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Toán: 9; Tiếng Việt: 8; Tiếng Anh: 7.9</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Diện Tuyển thẳng (không phải thi khảo sát đầu vào)</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C8" t="str">
-        <v>0601012314</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Phạm Nguyễn Minh Anh</v>
-      </c>
-      <c r="E8" t="str">
-        <v>10.2_CS1</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Khối 10</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Toán: 6; Ngữ Văn: 8.5; Tiếng Anh: 2.7 (Tổng: 26.7)</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Toán: 4.5; Ngữ Văn: 5</v>
-      </c>
-      <c r="K8" t="str">
-        <v>Dưới TB môn Toán (4.5), cần kèm gấp</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>4</v>
-      </c>
-      <c r="B9" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C9" t="str">
-        <v>0601012372</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Phan Đình Phùng</v>
-      </c>
-      <c r="E9" t="str">
-        <v>10.1_CS1</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Khối 10</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Tiếng Anh, Toán, Ngữ Văn</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Toán: 4; Ngữ Văn: 3; Tiếng Anh: 1.5 (Tổng: 15)</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Toán: 4.75; Ngữ Văn: 2; Tiếng Anh: 4.6</v>
-      </c>
-      <c r="K9" t="str">
-        <v>Bứt phá ngoạn mục (+3.1)</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>5</v>
-      </c>
-      <c r="B10" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C10" t="str">
-        <v>0601011201</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Mai Huy Thắng</v>
-      </c>
-      <c r="E10" t="str">
-        <v>7.1_CS1</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Khối 7</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Toán</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Thiếu môn CKĐV</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Ngữ Văn: 8; Tiếng Anh: 8.0 (Tổng: 80) (Toán: Chưa có điểm)</v>
-      </c>
-      <c r="J10" t="str">
-        <v>Toán: 8; Ngữ Văn: 7; Tiếng Anh: 8.8</v>
-      </c>
-      <c r="K10" t="str">
-        <v>Đạt chuẩn môn Anh (8.8)</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>6</v>
-      </c>
-      <c r="B11" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C11" t="str">
-        <v>0601012363</v>
-      </c>
-      <c r="D11" t="str">
-        <v xml:space="preserve">Phạm Thùy Gia Hân </v>
-      </c>
-      <c r="E11" t="str">
-        <v>10.2_CS1</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Khối 10</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Toán: 5; Ngữ Văn: 8; Tiếng Anh: 2.0 (Tổng: 20)</v>
-      </c>
-      <c r="J11" t="str">
-        <v>Toán: 7.25; Ngữ Văn: 5.5; Tiếng Anh: 4.7</v>
-      </c>
-      <c r="K11" t="str">
-        <v>Tiến bộ rõ rệt (+2.7)</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>7</v>
-      </c>
-      <c r="B12" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C12" t="str">
-        <v>0601012381</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Nguyễn Bình Phương An</v>
-      </c>
-      <c r="E12" t="str">
-        <v>10.1_CS1</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Khối 10</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I12" t="str">
-        <v>Tiếng Anh: 1.5 (Tổng: 15)</v>
-      </c>
-      <c r="J12" t="str">
-        <v>Toán: 6.25; Ngữ Văn: 5; Tiếng Anh: 4.8</v>
-      </c>
-      <c r="K12" t="str">
-        <v>Bứt phá ngoạn mục (+3.3)</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>8</v>
-      </c>
-      <c r="B13" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C13" t="str">
-        <v>0601050347</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Lê Bảo Trâm</v>
-      </c>
-      <c r="E13" t="str">
-        <v>7.3_CS1</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Khối 7</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I13" t="str">
-        <v>Tiếng Anh: 4.2 (Tổng: 42)</v>
-      </c>
-      <c r="J13" t="str">
-        <v>Toán: 8.3; Ngữ Văn: 7.5; Tiếng Anh: 4.9</v>
-      </c>
-      <c r="K13" t="str">
-        <v>Dưới TB môn Anh (4.9), cần phụ đạo</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>9</v>
-      </c>
-      <c r="B14" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C14" t="str">
-        <v>0601011593</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Lê Bảo Châu</v>
-      </c>
-      <c r="E14" t="str">
-        <v>9.3_CS1</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Khối 9</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Toán, Tiếng Anh</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I14" t="str">
-        <v>Toán: 2; Ngữ Văn: 6.5; Tiếng Anh: 1.9 (Tổng: 19)</v>
-      </c>
-      <c r="J14" t="str">
-        <v>Toán: 3.5; Ngữ Văn: 4.5; Tiếng Anh: 5.2</v>
-      </c>
-      <c r="K14" t="str">
-        <v>Bứt phá ngoạn mục (+3.3)</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>10</v>
-      </c>
-      <c r="B15" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C15" t="str">
-        <v>0601012376</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Phạm Gia Hương</v>
-      </c>
-      <c r="E15" t="str">
-        <v>10.2_CS1</v>
-      </c>
-      <c r="F15" t="str">
-        <v>Khối 10</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Tiếng Anh, Toán</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I15" t="str">
-        <v>Toán: 3; Ngữ Văn: 7.25; Tiếng Anh: 3.8 (Tổng: 38)</v>
-      </c>
-      <c r="J15" t="str">
-        <v>Toán: 4; Ngữ Văn: 6.5; Tiếng Anh: 5.1</v>
-      </c>
-      <c r="K15" t="str">
-        <v>Tiến bộ rõ rệt (+1.3)</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>11</v>
-      </c>
-      <c r="B16" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C16" t="str">
-        <v>0601012390</v>
-      </c>
-      <c r="D16" t="str">
-        <v xml:space="preserve">Đỗ An Nhiên </v>
-      </c>
-      <c r="E16" t="str">
-        <v>1.1_CS1</v>
-      </c>
-      <c r="F16" t="str">
-        <v>Khối 1</v>
-      </c>
-      <c r="G16" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I16" t="str">
-        <v>Tiếng Anh: 1.0 (Tổng: 10)</v>
-      </c>
-      <c r="J16" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>12</v>
-      </c>
-      <c r="B17" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C17" t="str">
-        <v>0602040631</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Hà Đặng Phước Huy</v>
-      </c>
-      <c r="E17" t="str">
-        <v>1S_CS4</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Khối 1</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H17" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I17" t="str">
-        <v>Tiếng Anh: 3.3 (Tổng: 33.3)</v>
-      </c>
-      <c r="J17" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>13</v>
-      </c>
-      <c r="B18" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C18" t="str">
-        <v>0601012396</v>
-      </c>
-      <c r="D18" t="str">
-        <v xml:space="preserve">Trần Hoàng Anh </v>
-      </c>
-      <c r="E18" t="str">
-        <v>9.2_CS1</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Khối 9</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Tiếng Anh, Toán</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Thiếu môn CKĐV</v>
-      </c>
-      <c r="I18" t="str">
-        <v>Toán: 4; Ngữ Văn: 6.5 (Tiếng Anh: Chưa có điểm)</v>
-      </c>
-      <c r="J18" t="str">
-        <v>Toán: 6.5; Ngữ Văn: 6; Tiếng Anh: 4</v>
-      </c>
-      <c r="K18" t="str">
-        <v>Tiến bộ tốt môn Toán (+2.5)</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>14</v>
-      </c>
-      <c r="B19" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C19" t="str">
-        <v>0701010055</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Nguyễn Ngọc Thiên Bảo</v>
-      </c>
-      <c r="E19" t="str">
-        <v>2.3INT_CS1</v>
-      </c>
-      <c r="F19" t="str">
-        <v>Khối 2</v>
-      </c>
-      <c r="G19" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I19" t="str">
-        <v>Tiếng Anh: 3.9 (Tổng: 39)</v>
-      </c>
-      <c r="J19" t="str">
-        <v>Tiếng Việt: 8; Tiếng Anh: 4</v>
-      </c>
-      <c r="K19" t="str">
-        <v>Chưa đạt chuẩn Tiểu học (4)</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>15</v>
-      </c>
-      <c r="B20" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C20" t="str">
-        <v>0601012393</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Nguyễn Thanh Thảo</v>
-      </c>
-      <c r="E20" t="str">
-        <v>9.4_CS1</v>
-      </c>
-      <c r="F20" t="str">
-        <v>Khối 9</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Chưa có điểm KSĐV</v>
-      </c>
-      <c r="I20" t="str">
-        <v>Chưa có điểm KSĐV (Chưa cập nhật điểm bài thi Tiếng Anh trên hệ thống)</v>
-      </c>
-      <c r="J20" t="str">
-        <v>Toán: 5; Ngữ Văn: 5.5; Tiếng Anh: 4.6</v>
-      </c>
-      <c r="K20" t="str">
-        <v>Chưa cập nhật điểm bài thi Tiếng Anh trên hệ thống</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>16</v>
-      </c>
-      <c r="B21" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C21" t="str">
-        <v>0601011617</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Lê Khánh Hà</v>
-      </c>
-      <c r="E21" t="str">
-        <v>10.2_CS1</v>
-      </c>
-      <c r="F21" t="str">
-        <v>Khối 10</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Toán, Tiếng Anh</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Thiếu môn CKĐV</v>
-      </c>
-      <c r="I21" t="str">
-        <v>Toán: 4; Ngữ Văn: 7 (Tiếng Anh: Chưa có điểm)</v>
-      </c>
-      <c r="J21" t="str">
-        <v>Toán: 7; Ngữ Văn: 4.5; Tiếng Anh: 4</v>
-      </c>
-      <c r="K21" t="str">
-        <v>Tiến bộ tốt môn Toán (+3)</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>17</v>
-      </c>
-      <c r="B22" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C22" t="str">
-        <v>0601012394</v>
-      </c>
-      <c r="D22" t="str">
-        <v xml:space="preserve">Nguyễn Đại Phúc </v>
-      </c>
-      <c r="E22" t="str">
-        <v>10.1_CS1</v>
-      </c>
-      <c r="F22" t="str">
-        <v>Khối 10</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I22" t="str">
-        <v>Tiếng Anh: 4.4 (Tổng: 44)</v>
-      </c>
-      <c r="J22" t="str">
-        <v>Toán: 6.1; Ngữ Văn: 7; Tiếng Anh: 6.2</v>
-      </c>
-      <c r="K22" t="str">
-        <v>Tiến bộ rõ rệt (+1.8)</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>18</v>
-      </c>
-      <c r="B23" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C23" t="str">
-        <v>HS331</v>
-      </c>
-      <c r="D23" t="str">
-        <v>LÊ ĐÌNH SĨ PHÚ</v>
-      </c>
-      <c r="E23" t="str">
-        <v>6.1_CS1</v>
-      </c>
-      <c r="F23" t="str">
-        <v>Khối 6</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Toán</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I23" t="str">
-        <v>Toán: 4; Tiếng Việt: 5; Ngữ Văn: 5; Tiếng Anh: 5.0 (Tổng: 50)</v>
-      </c>
-      <c r="J23" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>19</v>
-      </c>
-      <c r="B24" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C24" t="str">
-        <v>0601012399</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Ngô Thục Đan</v>
-      </c>
-      <c r="E24" t="str">
-        <v>9.1_CS1</v>
-      </c>
-      <c r="F24" t="str">
-        <v>Khối 9</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Tâm lý</v>
-      </c>
-      <c r="H24" t="str">
-        <v>Cam kết Tâm lý</v>
-      </c>
-      <c r="I24" t="str">
-        <v>HS Cam kết tâm lý</v>
-      </c>
-      <c r="J24" t="str">
-        <v>—</v>
-      </c>
-      <c r="K24" t="str">
-        <v>Theo dõi phát triển tâm lý lứa tuổi</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>20</v>
-      </c>
-      <c r="B25" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C25" t="str">
-        <v>0601012317</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Lê Nguyệt Cát</v>
-      </c>
-      <c r="E25" t="str">
-        <v>7.4_CS1</v>
-      </c>
-      <c r="F25" t="str">
-        <v>Khối 7</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I25" t="str">
-        <v>Toán: 5; Ngữ Văn: 6.5; Tiếng Anh: 2.6 (Tổng: 26)</v>
-      </c>
-      <c r="J25" t="str">
-        <v>Toán: 5.3; Ngữ Văn: 8; Tiếng Anh: 3.7</v>
-      </c>
-      <c r="K25" t="str">
-        <v>Tiến bộ rõ rệt (+1.1)</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>21</v>
-      </c>
-      <c r="B26" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C26" t="str">
-        <v>0601012338</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Hoàng Bảo Quyên</v>
-      </c>
-      <c r="E26" t="str">
-        <v>9.2_CS1</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Khối 9</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I26" t="str">
-        <v>Tiếng Anh: 2.2 (Tổng: 22)</v>
-      </c>
-      <c r="J26" t="str">
-        <v>Toán: 5.25; Ngữ Văn: 4; Tiếng Anh: 4.6</v>
-      </c>
-      <c r="K26" t="str">
-        <v>Tiến bộ rõ rệt (+2.4)</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>22</v>
-      </c>
-      <c r="B27" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C27" t="str">
-        <v>0601012280</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Phạm Gia Bảo</v>
-      </c>
-      <c r="E27" t="str">
-        <v>9.3_CS1</v>
-      </c>
-      <c r="F27" t="str">
-        <v>Khối 9</v>
-      </c>
-      <c r="G27" t="str">
-        <v>Tiếng Anh, Toán</v>
-      </c>
-      <c r="H27" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I27" t="str">
-        <v>Toán: 4; Ngữ Văn: 6.5; Tiếng Anh: 1.0 (Tổng: 10)</v>
-      </c>
-      <c r="J27" t="str">
-        <v>Toán: 3.75; Ngữ Văn: 3.5; Tiếng Anh: 3.6</v>
-      </c>
-      <c r="K27" t="str">
-        <v>Tiến bộ rõ rệt (+2.6)</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>23</v>
-      </c>
-      <c r="B28" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C28" t="str">
-        <v>0601012318</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Đặng Hoàng Như Ý</v>
-      </c>
-      <c r="E28" t="str">
-        <v>10.2_CS1</v>
-      </c>
-      <c r="F28" t="str">
-        <v>Khối 10</v>
-      </c>
-      <c r="G28" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H28" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I28" t="str">
-        <v>Tiếng Anh: 4.6 (Tổng: 46)</v>
-      </c>
-      <c r="J28" t="str">
-        <v>Toán: 6.75; Ngữ Văn: 6.8</v>
-      </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>24</v>
-      </c>
-      <c r="B29" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C29" t="str">
-        <v>0601012334</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Phạm Hải Như</v>
-      </c>
-      <c r="E29" t="str">
-        <v>10.2_CS1</v>
-      </c>
-      <c r="F29" t="str">
-        <v>Khối 10</v>
-      </c>
-      <c r="G29" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H29" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I29" t="str">
-        <v>Toán: 5; Ngữ Văn: 5; Tiếng Anh: 4.6 (Tổng: 46)</v>
-      </c>
-      <c r="J29" t="str">
-        <v>Toán: 4.25; Ngữ Văn: 4.3; Tiếng Anh: 4.6</v>
-      </c>
-      <c r="K29" t="str">
-        <v>Dưới TB môn Anh (4.6), cần phụ đạo</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>25</v>
-      </c>
-      <c r="B30" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C30" t="str">
-        <v>0701030403</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Nguyễn Thành Long</v>
-      </c>
-      <c r="E30" t="str">
-        <v>7.3_CS1</v>
-      </c>
-      <c r="F30" t="str">
-        <v>Khối 9</v>
-      </c>
-      <c r="G30" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H30" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I30" t="str">
-        <v>Ngữ Văn: 8.25; Tiếng Anh: 2.8 (Tổng: 28)</v>
-      </c>
-      <c r="J30" t="str">
-        <v>Toán: 4; Ngữ Văn: 4.5; Tiếng Anh: 5.1</v>
-      </c>
-      <c r="K30" t="str">
-        <v>Tiến bộ rõ rệt (+2.3)</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>26</v>
-      </c>
-      <c r="B31" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C31" t="str">
-        <v>0601012369</v>
-      </c>
-      <c r="D31" t="str">
-        <v>Trần Quang Thiên Ân</v>
-      </c>
-      <c r="E31" t="str">
-        <v>10.1_CS1</v>
-      </c>
-      <c r="F31" t="str">
-        <v>Khối 10</v>
-      </c>
-      <c r="G31" t="str">
-        <v>Toán</v>
-      </c>
-      <c r="H31" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I31" t="str">
-        <v>Toán: 3; Ngữ Văn: 6.5; Tiếng Anh: 7.7 (Tổng: 77)</v>
-      </c>
-      <c r="J31" t="str">
-        <v>Toán: 7.25; Ngữ Văn: 4; Tiếng Anh: 9</v>
-      </c>
-      <c r="K31" t="str">
-        <v>Tiến bộ rõ rệt (+1.3)</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>27</v>
-      </c>
-      <c r="B32" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C32" t="str">
-        <v>0601012312</v>
-      </c>
-      <c r="D32" t="str">
-        <v>Lê Hồ Gia Huy</v>
-      </c>
-      <c r="E32" t="str">
-        <v>10.2_CS1</v>
-      </c>
-      <c r="F32" t="str">
-        <v>Khối 10</v>
-      </c>
-      <c r="G32" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H32" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I32" t="str">
-        <v>Tiếng Anh: 2.7 (Tổng: 27)</v>
-      </c>
-      <c r="J32" t="str">
-        <v>Toán: 4.5; Ngữ Văn: 5; Tiếng Anh: 4.4</v>
-      </c>
-      <c r="K32" t="str">
-        <v>Tiến bộ rõ rệt (+1.7)</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>28</v>
-      </c>
-      <c r="B33" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C33" t="str">
-        <v>0601012400</v>
-      </c>
-      <c r="D33" t="str">
-        <v>Trương Lê Hưng Phát</v>
-      </c>
-      <c r="E33" t="str">
-        <v>12.1_CS1</v>
-      </c>
-      <c r="F33" t="str">
-        <v>Khối 12</v>
-      </c>
-      <c r="G33" t="str">
-        <v>Toán</v>
-      </c>
-      <c r="H33" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I33" t="str">
-        <v>Toán: 4; Ngữ Văn: 6.5; Tiếng Anh: 5.2 (Tổng: 52)</v>
-      </c>
-      <c r="J33" t="str">
-        <v>Toán: 5.1; Ngữ Văn: 3.5; Tiếng Anh: 5.5</v>
-      </c>
-      <c r="K33" t="str">
-        <v>Đạt chuẩn môn Anh (5.5)</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>29</v>
-      </c>
-      <c r="B34" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C34" t="str">
-        <v>0601012351</v>
-      </c>
-      <c r="D34" t="str">
-        <v>Nguyễn Văn Tuấn Kiệt</v>
-      </c>
-      <c r="E34" t="str">
-        <v>9.2_CS1</v>
-      </c>
-      <c r="F34" t="str">
-        <v>Khối 9</v>
-      </c>
-      <c r="G34" t="str">
-        <v>Toán, Tiếng Anh</v>
-      </c>
-      <c r="H34" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I34" t="str">
-        <v>Toán: 5; Ngữ Văn: 5.5; Tiếng Anh: 3.5 (Tổng: 35)</v>
-      </c>
-      <c r="J34" t="str">
-        <v>Toán: 3; Ngữ Văn: 4.5; Tiếng Anh: 2.9</v>
-      </c>
-      <c r="K34" t="str">
-        <v>Dưới TB môn Anh (2.9), cần phụ đạo</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>30</v>
-      </c>
-      <c r="B35" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C35" t="str">
-        <v>0601012303</v>
-      </c>
-      <c r="D35" t="str">
-        <v>Nguyễn Daniil</v>
-      </c>
-      <c r="E35" t="str">
-        <v>1.1_CS1</v>
-      </c>
-      <c r="F35" t="str">
-        <v>Khối 1</v>
-      </c>
-      <c r="G35" t="str">
-        <v>Tiếng Việt</v>
-      </c>
-      <c r="H35" t="str">
-        <v>Thiếu môn CKĐV</v>
-      </c>
-      <c r="I35" t="str">
-        <v>Tiếng Anh: 1.3 (Tổng: 13.3) (Tiếng Việt: Chưa có điểm)</v>
-      </c>
-      <c r="J35" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K35" t="str">
-        <v>Học sinh nước ngoài / song ngữ (chưa qua khảo sát Tiếng Việt đầu vào)</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>31</v>
-      </c>
-      <c r="B36" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C36" t="str">
-        <v>0601012340</v>
-      </c>
-      <c r="D36" t="str">
-        <v>Trần Đăng Quang</v>
-      </c>
-      <c r="E36" t="str">
-        <v>6.3_CS1</v>
-      </c>
-      <c r="F36" t="str">
-        <v>Khối 6</v>
-      </c>
-      <c r="G36" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H36" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I36" t="str">
-        <v>Toán: 10; Ngữ Văn: 7.5; Tiếng Anh: 4.3 (Tổng: 43)</v>
-      </c>
-      <c r="J36" t="str">
-        <v>Toán: 6.5; Ngữ Văn: 6.75; Tiếng Anh: 5.6</v>
-      </c>
-      <c r="K36" t="str">
-        <v>Tiến bộ rõ rệt (+1.3)</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>32</v>
-      </c>
-      <c r="B37" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C37" t="str">
-        <v>0601012347</v>
-      </c>
-      <c r="D37" t="str">
-        <v>Trần Thục Quyên</v>
-      </c>
-      <c r="E37" t="str">
-        <v>7.4_CS1</v>
-      </c>
-      <c r="F37" t="str">
-        <v>Khối 7</v>
-      </c>
-      <c r="G37" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H37" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I37" t="str">
-        <v>Tiếng Anh: 4.3 (Tổng: 43)</v>
-      </c>
-      <c r="J37" t="str">
-        <v>Toán: 9; Ngữ Văn: 7.5; Tiếng Anh: 6</v>
-      </c>
-      <c r="K37" t="str">
-        <v>Tiến bộ rõ rệt (+1.7)</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>33</v>
-      </c>
-      <c r="B38" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C38" t="str">
-        <v>0601012348</v>
-      </c>
-      <c r="D38" t="str">
-        <v>Lương Bích Ngọc</v>
-      </c>
-      <c r="E38" t="str">
-        <v>6.3_CS1</v>
-      </c>
-      <c r="F38" t="str">
-        <v>Khối 6</v>
-      </c>
-      <c r="G38" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H38" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I38" t="str">
-        <v>Toán: 4; Ngữ Văn: 8.5; Tiếng Anh: 4.3 (Tổng: 43)</v>
-      </c>
-      <c r="J38" t="str">
-        <v>Toán: 6.8; Ngữ Văn: 7.25; Tiếng Anh: 5</v>
-      </c>
-      <c r="K38" t="str">
-        <v>Đạt chuẩn môn Anh (5)</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>34</v>
-      </c>
-      <c r="B39" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C39" t="str">
-        <v>0601011972</v>
-      </c>
-      <c r="D39" t="str">
-        <v>Nguyễn Quỳnh Như</v>
-      </c>
-      <c r="E39" t="str">
-        <v>3.1_CS1</v>
-      </c>
-      <c r="F39" t="str">
-        <v>Khối 6</v>
-      </c>
-      <c r="G39" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H39" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I39" t="str">
-        <v>Toán: 3; Ngữ Văn: 7; Tiếng Anh: 3.9 (Tổng: 39)</v>
-      </c>
-      <c r="J39" t="str">
-        <v>Toán: 5; Tiếng Việt: 9.5; Ngữ Văn: 7; Tiếng Anh: 9.1</v>
-      </c>
-      <c r="K39" t="str">
-        <v>Bứt phá ngoạn mục (+5.2)</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>35</v>
-      </c>
-      <c r="B40" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C40" t="str">
-        <v>0601012153</v>
-      </c>
-      <c r="D40" t="str">
-        <v>Nguyễn Ngọc Minh</v>
-      </c>
-      <c r="E40" t="str">
-        <v>7.2_CS1</v>
-      </c>
-      <c r="F40" t="str">
-        <v>Khối 7</v>
-      </c>
-      <c r="G40" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H40" t="str">
-        <v>Thiếu môn CKĐV</v>
-      </c>
-      <c r="I40" t="str">
-        <v>Toán: 6; Ngữ Văn: 7 (Tiếng Anh: Chưa có điểm)</v>
-      </c>
-      <c r="J40" t="str">
-        <v>Toán: 8.75; Ngữ Văn: 5.75; Tiếng Anh: 4.1</v>
-      </c>
-      <c r="K40" t="str">
-        <v>Tiến bộ tốt môn Toán (+2.8)</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>36</v>
-      </c>
-      <c r="B41" t="str">
-        <v>CS1</v>
-      </c>
-      <c r="C41" t="str">
-        <v>0601012421</v>
-      </c>
-      <c r="D41" t="str">
-        <v xml:space="preserve">Nguyễn Đặng Bảo Trâm </v>
-      </c>
-      <c r="E41" t="str">
-        <v>8.2_CS1</v>
-      </c>
-      <c r="F41" t="str">
-        <v>Khối 8</v>
-      </c>
-      <c r="G41" t="str">
-        <v>Chung / Theo dõi</v>
-      </c>
-      <c r="H41" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I41" t="str">
-        <v>Toán: 7; Ngữ Văn: 6.5; Tiếng Anh: 4.8 (Tổng: 48)</v>
-      </c>
-      <c r="J41" t="str">
-        <v>Toán: 3; Ngữ Văn: 6.5; Tiếng Anh: 4</v>
-      </c>
-      <c r="K41" t="str">
-        <v>Dưới TB môn Anh (4), cần phụ đạo</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>37</v>
-      </c>
-      <c r="B42" t="str">
-        <v>CS2</v>
-      </c>
-      <c r="C42" t="str">
-        <v>0601021777</v>
-      </c>
-      <c r="D42" t="str">
-        <v>Lê Gia Lân</v>
-      </c>
-      <c r="E42" t="str">
-        <v>1.3_CS2</v>
-      </c>
-      <c r="F42" t="str">
-        <v>Khối 1</v>
-      </c>
-      <c r="G42" t="str">
-        <v>Tâm lý</v>
-      </c>
-      <c r="H42" t="str">
-        <v>Cam kết Tâm lý</v>
-      </c>
-      <c r="I42" t="str">
-        <v>HS Cam kết tâm lý</v>
-      </c>
-      <c r="J42" t="str">
-        <v>—</v>
-      </c>
-      <c r="K42" t="str">
-        <v>Theo dõi phát triển tâm lý lứa tuổi</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>38</v>
-      </c>
-      <c r="B43" t="str">
-        <v>CS2</v>
-      </c>
-      <c r="C43" t="str">
-        <v>0601021457</v>
-      </c>
-      <c r="D43" t="str">
-        <v>Đào Trần Thảo Linh</v>
-      </c>
-      <c r="E43" t="str">
-        <v>1.3_CS2</v>
-      </c>
-      <c r="F43" t="str">
-        <v>Khối 1</v>
-      </c>
-      <c r="G43" t="str">
-        <v>Tâm lý, Tiếng Việt</v>
-      </c>
-      <c r="H43" t="str">
-        <v>Cam kết Tâm lý</v>
-      </c>
-      <c r="I43" t="str">
-        <v>HS Cam kết tâm lý</v>
-      </c>
-      <c r="J43" t="str">
-        <v>—</v>
-      </c>
-      <c r="K43" t="str">
-        <v>Theo dõi phát triển tâm lý lứa tuổi</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>39</v>
-      </c>
-      <c r="B44" t="str">
-        <v>CS2</v>
-      </c>
-      <c r="C44" t="str">
-        <v>0701020104</v>
-      </c>
-      <c r="D44" t="str">
-        <v>Nguyễn Thanh Phúc</v>
-      </c>
-      <c r="E44" t="str">
-        <v>1.2INT_CS2</v>
-      </c>
-      <c r="F44" t="str">
-        <v>Khối 1</v>
-      </c>
-      <c r="G44" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H44" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I44" t="str">
-        <v>Tiếng Anh: 1.7 (Tổng: 16.7)</v>
-      </c>
-      <c r="J44" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K44" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>40</v>
-      </c>
-      <c r="B45" t="str">
-        <v>CS2</v>
-      </c>
-      <c r="C45" t="str">
-        <v>0601021794</v>
-      </c>
-      <c r="D45" t="str">
-        <v>ĐỖ NGUYỄN AN KHÔI</v>
-      </c>
-      <c r="E45" t="str">
-        <v>1.3_CS2</v>
-      </c>
-      <c r="F45" t="str">
-        <v>Khối 1</v>
-      </c>
-      <c r="G45" t="str">
-        <v>Chung / Theo dõi</v>
-      </c>
-      <c r="H45" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I45" t="str">
-        <v>Tiếng Anh: 2.3 (Tổng: 23.3)</v>
-      </c>
-      <c r="J45" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K45" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>41</v>
-      </c>
-      <c r="B46" t="str">
-        <v>CS2</v>
-      </c>
-      <c r="C46" t="str">
-        <v>0601021828</v>
-      </c>
-      <c r="D46" t="str">
-        <v>Phan Hải Đăng</v>
-      </c>
-      <c r="E46" t="str">
-        <v>1.3_CS2</v>
-      </c>
-      <c r="F46" t="str">
-        <v>Khối 1</v>
-      </c>
-      <c r="G46" t="str">
-        <v>Chung / Theo dõi</v>
-      </c>
-      <c r="H46" t="str">
-        <v>Chưa có điểm KSĐV</v>
-      </c>
-      <c r="I46" t="str">
-        <v>Chưa có điểm KSĐV (Cam kết theo dõi phát triển ngôn ngữ (chưa thi khảo sát văn hóa))</v>
-      </c>
-      <c r="J46" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K46" t="str">
-        <v>Cam kết theo dõi phát triển ngôn ngữ (chưa thi khảo sát văn hóa)</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>42</v>
-      </c>
-      <c r="B47" t="str">
-        <v>CS2</v>
-      </c>
-      <c r="C47" t="str">
-        <v>0601012037</v>
-      </c>
-      <c r="D47" t="str">
-        <v>Hoàng Bữu Minh Hưng</v>
-      </c>
-      <c r="E47" t="str">
-        <v>3.4_CS2</v>
-      </c>
-      <c r="F47" t="str">
-        <v>Khối 3</v>
-      </c>
-      <c r="G47" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H47" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I47" t="str">
-        <v>Tiếng Anh: 4.2 (Tổng: 42)</v>
-      </c>
-      <c r="J47" t="str">
-        <v>Toán: 8; Tiếng Việt: 8; Tiếng Anh: 5.5</v>
-      </c>
-      <c r="K47" t="str">
-        <v>Tiến bộ rõ rệt (+1.3)</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>43</v>
-      </c>
-      <c r="B48" t="str">
-        <v>CS2</v>
-      </c>
-      <c r="C48" t="str">
-        <v>0601021795</v>
-      </c>
-      <c r="D48" t="str">
-        <v>Lê Hồ Duy Khang</v>
-      </c>
-      <c r="E48" t="str">
-        <v>1.3_CS2</v>
-      </c>
-      <c r="F48" t="str">
-        <v>Khối 1</v>
-      </c>
-      <c r="G48" t="str">
-        <v>Tâm lý</v>
-      </c>
-      <c r="H48" t="str">
-        <v>Cam kết Tâm lý</v>
-      </c>
-      <c r="I48" t="str">
-        <v>HS Cam kết tâm lý</v>
-      </c>
-      <c r="J48" t="str">
-        <v>—</v>
-      </c>
-      <c r="K48" t="str">
-        <v>Theo dõi phát triển tâm lý lứa tuổi</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>44</v>
-      </c>
-      <c r="B49" t="str">
-        <v>CS2</v>
-      </c>
-      <c r="C49" t="str">
-        <v>0701020109</v>
-      </c>
-      <c r="D49" t="str">
-        <v>Sangadziev Aron</v>
-      </c>
-      <c r="E49" t="str">
-        <v>1.2INT_CS2</v>
-      </c>
-      <c r="F49" t="str">
-        <v>Khối 1</v>
-      </c>
-      <c r="G49" t="str">
-        <v>Tiếng Việt</v>
-      </c>
-      <c r="H49" t="str">
-        <v>Thiếu môn CKĐV</v>
-      </c>
-      <c r="I49" t="str">
-        <v>Tiếng Anh: 2.7 (Tổng: 26.7) (Tiếng Việt: Chưa có điểm)</v>
-      </c>
-      <c r="J49" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K49" t="str">
-        <v>Học sinh nước ngoài / song ngữ (chưa qua khảo sát Tiếng Việt đầu vào)</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>45</v>
-      </c>
-      <c r="B50" t="str">
-        <v>CS3</v>
-      </c>
-      <c r="C50" t="str">
-        <v>0701030370</v>
-      </c>
-      <c r="D50" t="str">
-        <v>Phan Anh Quân</v>
-      </c>
-      <c r="E50" t="str">
-        <v>9INT_CS3</v>
-      </c>
-      <c r="F50" t="str">
-        <v>Khối 9</v>
-      </c>
-      <c r="G50" t="str">
-        <v>Toán, Tiếng Anh</v>
-      </c>
-      <c r="H50" t="str">
-        <v>Thiếu môn CKĐV</v>
-      </c>
-      <c r="I50" t="str">
-        <v>Ngữ Văn: 5; Tiếng Anh: 4.1 (Tổng: 41) (Toán: Chưa có điểm)</v>
-      </c>
-      <c r="J50" t="str">
-        <v>Toán: 6.25; Ngữ Văn: 6; Tiếng Anh: 5.6</v>
-      </c>
-      <c r="K50" t="str">
-        <v>Tiến bộ rõ rệt (+1.5)</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>46</v>
-      </c>
-      <c r="B51" t="str">
-        <v>CS3</v>
-      </c>
-      <c r="C51" t="str">
-        <v>0701030387</v>
-      </c>
-      <c r="D51" t="str">
-        <v>Đoàn Ngọc Thảo Chloe</v>
-      </c>
-      <c r="E51" t="str">
-        <v>2.1INT_CS3</v>
-      </c>
-      <c r="F51" t="str">
-        <v>Khối 2</v>
-      </c>
-      <c r="G51" t="str">
-        <v>Tiếng Việt, Tiếng Anh</v>
-      </c>
-      <c r="H51" t="str">
-        <v>Thiếu môn CKĐV</v>
-      </c>
-      <c r="I51" t="str">
-        <v>Tiếng Anh: 8.4 (Tổng: 84) (Tiếng Việt: Chưa có điểm)</v>
-      </c>
-      <c r="J51" t="str">
-        <v>Tiếng Việt: 4; Tiếng Anh: 9.8</v>
-      </c>
-      <c r="K51" t="str">
-        <v>Tiến bộ rõ rệt (+1.4)</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>47</v>
-      </c>
-      <c r="B52" t="str">
-        <v>CS3</v>
-      </c>
-      <c r="C52" t="str">
-        <v>0501030625</v>
-      </c>
-      <c r="D52" t="str">
-        <v>Hồ Hữu Bách</v>
-      </c>
-      <c r="E52" t="str">
-        <v>4UK_CS3</v>
-      </c>
-      <c r="F52" t="str">
-        <v>Khối 4</v>
-      </c>
-      <c r="G52" t="str">
-        <v>Tiếng Việt</v>
-      </c>
-      <c r="H52" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I52" t="str">
-        <v>Tiếng Việt: 3; Tiếng Anh: 8.2 (Tổng: 82)</v>
-      </c>
-      <c r="J52" t="str">
-        <v>Tiếng Việt: 1.5; Tiếng Anh: 7.8</v>
-      </c>
-      <c r="K52" t="str">
-        <v>Đạt chuẩn môn Anh (7.8)</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>48</v>
-      </c>
-      <c r="B53" t="str">
-        <v>CS3</v>
-      </c>
-      <c r="C53" t="str">
-        <v>0701030397</v>
-      </c>
-      <c r="D53" t="str">
-        <v>Govorushko Mikhail</v>
-      </c>
-      <c r="E53" t="str">
-        <v>1.1INT_CS3</v>
-      </c>
-      <c r="F53" t="str">
-        <v>Khối 1</v>
-      </c>
-      <c r="G53" t="str">
-        <v>Tiếng Việt</v>
-      </c>
-      <c r="H53" t="str">
-        <v>Thiếu môn CKĐV</v>
-      </c>
-      <c r="I53" t="str">
-        <v>Tiếng Anh: 3.2 (Tổng: 31.7) (Tiếng Việt: Chưa có điểm)</v>
-      </c>
-      <c r="J53" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K53" t="str">
-        <v>Học sinh nước ngoài / song ngữ (chưa qua khảo sát Tiếng Việt đầu vào)</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>49</v>
-      </c>
-      <c r="B54" t="str">
-        <v>CS3</v>
-      </c>
-      <c r="C54" t="str">
-        <v>0701030402</v>
-      </c>
-      <c r="D54" t="str">
-        <v>Lecomte Mailys Mộc Yên</v>
-      </c>
-      <c r="E54" t="str">
-        <v>4INT_CS3</v>
-      </c>
-      <c r="F54" t="str">
-        <v>Khối 4</v>
-      </c>
-      <c r="G54" t="str">
-        <v>Tiếng Việt, Tiếng Anh</v>
-      </c>
-      <c r="H54" t="str">
-        <v>Thiếu môn CKĐV</v>
-      </c>
-      <c r="I54" t="str">
-        <v>Tiếng Anh: 9.6 (Tổng: 96) (Tiếng Việt: Chưa có điểm)</v>
-      </c>
-      <c r="J54" t="str">
-        <v>Tiếng Việt: 5; Tiếng Anh: 7.3</v>
-      </c>
-      <c r="K54" t="str">
-        <v>Đạt chuẩn môn Anh (7.3)</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>50</v>
-      </c>
-      <c r="B55" t="str">
-        <v>CS3</v>
-      </c>
-      <c r="C55" t="str">
-        <v>0701030384</v>
-      </c>
-      <c r="D55" t="str">
-        <v>Hà Minh Khuê</v>
-      </c>
-      <c r="E55" t="str">
-        <v>5.1INT_CS3</v>
-      </c>
-      <c r="F55" t="str">
-        <v>Khối 5</v>
-      </c>
-      <c r="G55" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H55" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I55" t="str">
-        <v>Tiếng Việt: 7; Tiếng Anh: 4.6 (Tổng: 46)</v>
-      </c>
-      <c r="J55" t="str">
-        <v>Tiếng Việt: 9; Tiếng Anh: 3.6</v>
-      </c>
-      <c r="K55" t="str">
-        <v>Chưa đạt chuẩn Tiểu học (3.6)</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>51</v>
-      </c>
-      <c r="B56" t="str">
-        <v>CS3</v>
-      </c>
-      <c r="C56" t="str">
-        <v>0701030415</v>
-      </c>
-      <c r="D56" t="str">
-        <v>Phùng Đức Thiên Ân</v>
-      </c>
-      <c r="E56" t="str">
-        <v>3.1INT_CS3</v>
-      </c>
-      <c r="F56" t="str">
-        <v>Khối 3</v>
-      </c>
-      <c r="G56" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H56" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I56" t="str">
-        <v>Tiếng Anh: 3.6 (Tổng: 36)</v>
-      </c>
-      <c r="J56" t="str">
-        <v>Tiếng Việt: 6; Tiếng Anh: 6.55</v>
-      </c>
-      <c r="K56" t="str">
-        <v>Tiến bộ rõ rệt (+2.9)</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>52</v>
-      </c>
-      <c r="B57" t="str">
-        <v>CS3</v>
-      </c>
-      <c r="C57" t="str">
-        <v>0701030416</v>
-      </c>
-      <c r="D57" t="str">
-        <v>Phùng Chí Nam Anh</v>
-      </c>
-      <c r="E57" t="str">
-        <v>8.1INT_CS3</v>
-      </c>
-      <c r="F57" t="str">
-        <v>Khối 8</v>
-      </c>
-      <c r="G57" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H57" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I57" t="str">
-        <v>Tiếng Anh: 3.0 (Tổng: 30)</v>
-      </c>
-      <c r="J57" t="str">
-        <v>Ngữ Văn: 5; Tiếng Anh: 3.5</v>
-      </c>
-      <c r="K57" t="str">
-        <v>Dưới TB môn Anh (3.5), cần phụ đạo</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>53</v>
-      </c>
-      <c r="B58" t="str">
-        <v>CS4</v>
-      </c>
-      <c r="C58" t="str">
-        <v>0602040593</v>
-      </c>
-      <c r="D58" t="str">
-        <v>Ayesha Mirza</v>
-      </c>
-      <c r="E58" t="str">
-        <v>6S_CS4</v>
-      </c>
-      <c r="F58" t="str">
-        <v>Khối 6</v>
-      </c>
-      <c r="G58" t="str">
-        <v>Toán, Tiếng Việt</v>
-      </c>
-      <c r="H58" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I58" t="str">
-        <v>Toán: 4; Ngữ Văn: 4; Tiếng Anh: 6.3 (Tổng: 63)</v>
-      </c>
-      <c r="J58" t="str">
-        <v>Toán: 3.8; Ngữ Văn: 2.25; Tiếng Anh: 3.7</v>
-      </c>
-      <c r="K58" t="str">
-        <v>Dưới TB môn Anh (3.7), cần phụ đạo</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>54</v>
-      </c>
-      <c r="B59" t="str">
-        <v>CS4</v>
-      </c>
-      <c r="C59" t="str">
-        <v>0602040630</v>
-      </c>
-      <c r="D59" t="str">
-        <v>HÀ ĐẶNG BẢO NGỌC</v>
-      </c>
-      <c r="E59" t="str">
-        <v>3S_CS4</v>
-      </c>
-      <c r="F59" t="str">
-        <v>Khối 3</v>
-      </c>
-      <c r="G59" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H59" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I59" t="str">
-        <v>Toán: 9; Tiếng Việt: 6; Tiếng Anh: 4.0 (Tổng: 40)</v>
-      </c>
-      <c r="J59" t="str">
-        <v>Toán: 8.3; Tiếng Việt: 7; Tiếng Anh: 2.8</v>
-      </c>
-      <c r="K59" t="str">
-        <v>Chưa đạt chuẩn Tiểu học (2.8)</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>55</v>
-      </c>
-      <c r="B60" t="str">
-        <v>CS4</v>
-      </c>
-      <c r="C60" t="str">
-        <v>0601012397</v>
-      </c>
-      <c r="D60" t="str">
-        <v>Nguyễn Thị Thu Thúy</v>
-      </c>
-      <c r="E60" t="str">
-        <v>10S_CS4</v>
-      </c>
-      <c r="F60" t="str">
-        <v>Khối 10</v>
-      </c>
-      <c r="G60" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H60" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I60" t="str">
-        <v>Toán: 5; Ngữ Văn: 5.5; Tiếng Anh: 1.8 (Tổng: 18)</v>
-      </c>
-      <c r="J60" t="str">
-        <v>Toán: 4.25; Ngữ Văn: 4; Tiếng Anh: 1.9</v>
-      </c>
-      <c r="K60" t="str">
-        <v>Dưới TB môn Anh (1.9), cần phụ đạo</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>56</v>
-      </c>
-      <c r="B61" t="str">
-        <v>CS4</v>
-      </c>
-      <c r="C61" t="str">
-        <v>0602040636</v>
-      </c>
-      <c r="D61" t="str">
-        <v>Huỳnh Hoàng An</v>
-      </c>
-      <c r="E61" t="str">
-        <v>3S_CS4</v>
-      </c>
-      <c r="F61" t="str">
-        <v>Khối 3</v>
-      </c>
-      <c r="G61" t="str">
-        <v>Toán, Tiếng Việt, Tiếng Anh</v>
-      </c>
-      <c r="H61" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I61" t="str">
-        <v>Toán: 5; Tiếng Việt: 4.5; Tiếng Anh: 8.7 (Tổng: 87)</v>
-      </c>
-      <c r="J61" t="str">
-        <v>Toán: 8.3; Tiếng Việt: 3; Tiếng Anh: 9.8</v>
-      </c>
-      <c r="K61" t="str">
-        <v>Tiến bộ rõ rệt (+1.1)</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>57</v>
-      </c>
-      <c r="B62" t="str">
-        <v>CS4</v>
-      </c>
-      <c r="C62" t="str">
-        <v>0602040624</v>
-      </c>
-      <c r="D62" t="str">
-        <v>Đặng Ngọc Bảo Ngân</v>
-      </c>
-      <c r="E62" t="str">
-        <v>10S_CS4</v>
-      </c>
-      <c r="F62" t="str">
-        <v>Khối 10</v>
-      </c>
-      <c r="G62" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H62" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I62" t="str">
-        <v>Tiếng Anh: 1.8 (Tổng: 18.4)</v>
-      </c>
-      <c r="J62" t="str">
-        <v>Toán: 3.5; Ngữ Văn: 2.5; Tiếng Anh: 2.5</v>
-      </c>
-      <c r="K62" t="str">
-        <v>Dưới TB môn Anh (2.5), cần phụ đạo</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>58</v>
-      </c>
-      <c r="B63" t="str">
-        <v>CS4</v>
-      </c>
-      <c r="C63" t="str">
-        <v>0602040623</v>
-      </c>
-      <c r="D63" t="str">
-        <v>Ngô Nhật Khang</v>
-      </c>
-      <c r="E63" t="str">
-        <v>10S_CS4</v>
-      </c>
-      <c r="F63" t="str">
-        <v>Khối 10</v>
-      </c>
-      <c r="G63" t="str">
-        <v>Tiếng Anh, Toán, Ngữ Văn</v>
-      </c>
-      <c r="H63" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I63" t="str">
-        <v>Toán: 4; Ngữ Văn: 4.5; Tiếng Anh: 1.8 (Tổng: 17.8)</v>
-      </c>
-      <c r="J63" t="str">
-        <v>Toán: 3.5; Ngữ Văn: 5.75; Tiếng Anh: 3.1</v>
-      </c>
-      <c r="K63" t="str">
-        <v>Tiến bộ rõ rệt (+1.3)</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>59</v>
-      </c>
-      <c r="B64" t="str">
-        <v>CS4</v>
-      </c>
-      <c r="C64" t="str">
-        <v>0602040522</v>
-      </c>
-      <c r="D64" t="str">
-        <v>Võ Hoàng Vi</v>
-      </c>
-      <c r="E64" t="str">
-        <v>6S_CS4</v>
-      </c>
-      <c r="F64" t="str">
-        <v>Khối 6</v>
-      </c>
-      <c r="G64" t="str">
-        <v>Toán</v>
-      </c>
-      <c r="H64" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I64" t="str">
-        <v>Toán: 3; Ngữ Văn: 5.25; Tiếng Anh: 8.5 (Tổng: 85)</v>
-      </c>
-      <c r="J64" t="str">
-        <v>Toán: 6.3; Ngữ Văn: 4.75; Tiếng Anh: 6.5</v>
-      </c>
-      <c r="K64" t="str">
-        <v>Đạt chuẩn môn Anh (6.5)</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>60</v>
-      </c>
-      <c r="B65" t="str">
-        <v>CS4</v>
-      </c>
-      <c r="C65" t="str">
-        <v>0602040642</v>
-      </c>
-      <c r="D65" t="str">
-        <v>Võ Như Quỳnh</v>
-      </c>
-      <c r="E65" t="str">
-        <v>7S_CS4</v>
-      </c>
-      <c r="F65" t="str">
-        <v>Khối 7</v>
-      </c>
-      <c r="G65" t="str">
-        <v>Toán, Ngữ Văn, Tiếng Anh</v>
-      </c>
-      <c r="H65" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I65" t="str">
-        <v>Toán: 4.5; Ngữ Văn: 5; Tiếng Anh: 4.2 (Tổng: 42)</v>
-      </c>
-      <c r="J65" t="str">
-        <v>Toán: 6; Ngữ Văn: 6; Tiếng Anh: 2.9</v>
-      </c>
-      <c r="K65" t="str">
-        <v>Dưới TB môn Anh (2.9), cần phụ đạo</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>61</v>
-      </c>
-      <c r="B66" t="str">
-        <v>CS4</v>
-      </c>
-      <c r="C66" t="str">
-        <v>0602040613</v>
-      </c>
-      <c r="D66" t="str">
-        <v>Đỗ Thành Nguyên</v>
-      </c>
-      <c r="E66" t="str">
-        <v>10S_CS4</v>
-      </c>
-      <c r="F66" t="str">
-        <v>Khối 10</v>
-      </c>
-      <c r="G66" t="str">
-        <v>Toán, Ngữ Văn, Tiếng Anh</v>
-      </c>
-      <c r="H66" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I66" t="str">
-        <v>Toán: 1.5; Ngữ Văn: 5; Tiếng Anh: 1.0 (Tổng: 10)</v>
-      </c>
-      <c r="J66" t="str">
-        <v>Toán: 0</v>
-      </c>
-      <c r="K66" t="str">
-        <v>Dưới TB môn Toán (0), cần kèm gấp</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>62</v>
-      </c>
-      <c r="B67" t="str">
-        <v>CS4</v>
-      </c>
-      <c r="C67" t="str">
-        <v>0602040586</v>
-      </c>
-      <c r="D67" t="str">
-        <v>Phạm Kiều Anh</v>
-      </c>
-      <c r="E67" t="str">
-        <v>6S_CS4</v>
-      </c>
-      <c r="F67" t="str">
-        <v>Khối 6</v>
-      </c>
-      <c r="G67" t="str">
-        <v>Ngữ Văn</v>
-      </c>
-      <c r="H67" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I67" t="str">
-        <v>Toán: 8; Tiếng Việt: 4; Ngữ Văn: 4; Tiếng Anh: 8.6 (Tổng: 86)</v>
-      </c>
-      <c r="J67" t="str">
-        <v>Toán: 9.3; Ngữ Văn: 7; Tiếng Anh: 7.3</v>
-      </c>
-      <c r="K67" t="str">
-        <v>Đạt chuẩn môn Anh (7.3)</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>63</v>
-      </c>
-      <c r="B68" t="str">
-        <v>CS4</v>
-      </c>
-      <c r="C68" t="str">
-        <v>0602040621</v>
-      </c>
-      <c r="D68" t="str">
-        <v>Võ Thị Anh Thư</v>
-      </c>
-      <c r="E68" t="str">
-        <v>7S_CS4</v>
-      </c>
-      <c r="F68" t="str">
-        <v>Khối 7</v>
-      </c>
-      <c r="G68" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H68" t="str">
-        <v>Thiếu môn CKĐV</v>
-      </c>
-      <c r="I68" t="str">
-        <v>Toán: 8 (Tiếng Anh: Chưa có điểm)</v>
-      </c>
-      <c r="J68" t="str">
-        <v>Toán: 4.3; Ngữ Văn: 7.5; Tiếng Anh: 2.6</v>
-      </c>
-      <c r="K68" t="str">
-        <v>Dưới TB môn Toán (4.3), cần kèm gấp</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>64</v>
-      </c>
-      <c r="B69" t="str">
-        <v>CS4</v>
-      </c>
-      <c r="C69" t="str">
-        <v>0602040655</v>
-      </c>
-      <c r="D69" t="str">
-        <v>Ngô Huỳnh Anh Minh</v>
-      </c>
-      <c r="E69" t="str">
-        <v>6S_CS4</v>
-      </c>
-      <c r="F69" t="str">
-        <v>Khối 6</v>
-      </c>
-      <c r="G69" t="str">
-        <v>Toán, Ngữ Văn</v>
-      </c>
-      <c r="H69" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I69" t="str">
-        <v>Toán: 4; Ngữ Văn: 5; Tiếng Anh: 9.6 (Tổng: 96)</v>
-      </c>
-      <c r="J69" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K69" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>65</v>
-      </c>
-      <c r="B70" t="str">
-        <v>CS5</v>
-      </c>
-      <c r="C70" t="str">
-        <v>0601051095</v>
-      </c>
-      <c r="D70" t="str">
-        <v>Mai Minh Minh</v>
-      </c>
-      <c r="E70" t="str">
-        <v>6.5_CS5</v>
-      </c>
-      <c r="F70" t="str">
-        <v>Khối 6</v>
-      </c>
-      <c r="G70" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H70" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I70" t="str">
-        <v>Tiếng Anh: 3.4 (Tổng: 34)</v>
-      </c>
-      <c r="J70" t="str">
-        <v>Toán: 4.25; Ngữ Văn: 7.5; Tiếng Anh: 4.5</v>
-      </c>
-      <c r="K70" t="str">
-        <v>Tiến bộ rõ rệt (+1.1)</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>66</v>
-      </c>
-      <c r="B71" t="str">
-        <v>CS5</v>
-      </c>
-      <c r="C71" t="str">
-        <v>0601051137</v>
-      </c>
-      <c r="D71" t="str">
-        <v>Lâm Minh Khang</v>
-      </c>
-      <c r="E71" t="str">
-        <v>2.5_CS5</v>
-      </c>
-      <c r="F71" t="str">
-        <v>Khối 2</v>
-      </c>
-      <c r="G71" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H71" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I71" t="str">
-        <v>Toán: 7; Tiếng Việt: 9; Tiếng Anh: 6.1 (Tổng: 61)</v>
-      </c>
-      <c r="J71" t="str">
-        <v>Toán: 9.5; Tiếng Việt: 7.3; Tiếng Anh: 6.1</v>
-      </c>
-      <c r="K71" t="str">
-        <v>Chưa đạt chuẩn Tiểu học (6.1)</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>67</v>
-      </c>
-      <c r="B72" t="str">
-        <v>CS5</v>
-      </c>
-      <c r="C72" t="str">
-        <v>0601051161</v>
-      </c>
-      <c r="D72" t="str">
-        <v>Đặng Ái Thiên Vân</v>
-      </c>
-      <c r="E72" t="str">
-        <v>3.6_CS5</v>
-      </c>
-      <c r="F72" t="str">
-        <v>Khối 3</v>
-      </c>
-      <c r="G72" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H72" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I72" t="str">
-        <v>Toán: 10; Tiếng Việt: 8; Tiếng Anh: 3.9 (Tổng: 39)</v>
-      </c>
-      <c r="J72" t="str">
-        <v>Toán: 10; Tiếng Việt: 9; Tiếng Anh: 5.6</v>
-      </c>
-      <c r="K72" t="str">
-        <v>Tiến bộ rõ rệt (+1.7)</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73">
-        <v>68</v>
-      </c>
-      <c r="B73" t="str">
-        <v>CS5</v>
-      </c>
-      <c r="C73" t="str">
-        <v>HS701020024</v>
-      </c>
-      <c r="D73" t="str">
-        <v>Bùi Tuấn Anh</v>
-      </c>
-      <c r="E73" t="str">
-        <v>7.5_CS5</v>
-      </c>
-      <c r="F73" t="str">
-        <v>Khối 7</v>
-      </c>
-      <c r="G73" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H73" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I73" t="str">
-        <v>Tiếng Anh: 2.0 (Tổng: 20)</v>
-      </c>
-      <c r="J73" t="str">
-        <v>Toán: 7.5; Ngữ Văn: 7.5; Tiếng Anh: 3.5</v>
-      </c>
-      <c r="K73" t="str">
-        <v>Tiến bộ rõ rệt (+1.5)</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74">
-        <v>69</v>
-      </c>
-      <c r="B74" t="str">
-        <v>CS5</v>
-      </c>
-      <c r="C74" t="str">
-        <v>0701030326</v>
-      </c>
-      <c r="D74" t="str">
-        <v>Phạm Gia Hưng</v>
-      </c>
-      <c r="E74" t="str">
-        <v>2.5_CS5</v>
-      </c>
-      <c r="F74" t="str">
-        <v>Khối 7</v>
-      </c>
-      <c r="G74" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H74" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I74" t="str">
-        <v>Toán: 2.3; Ngữ Văn: 4; Tiếng Anh: 2.6 (Tổng: 26)</v>
-      </c>
-      <c r="J74" t="str">
-        <v>Toán: 5; Tiếng Việt: 9.4; Ngữ Văn: 4.5; Tiếng Anh: 9.1</v>
-      </c>
-      <c r="K74" t="str">
-        <v>Bứt phá ngoạn mục (+6.5)</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75">
-        <v>70</v>
-      </c>
-      <c r="B75" t="str">
-        <v>CS5</v>
-      </c>
-      <c r="C75" t="str">
-        <v>0601051050</v>
-      </c>
-      <c r="D75" t="str">
-        <v>Vũ Đức Thịnh</v>
-      </c>
-      <c r="E75" t="str">
-        <v>1.5_CS5</v>
-      </c>
-      <c r="F75" t="str">
-        <v>Khối 1</v>
-      </c>
-      <c r="G75" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H75" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I75" t="str">
-        <v>Tiếng Anh: 1.0 (Tổng: 10)</v>
-      </c>
-      <c r="J75" t="str">
-        <v>Chưa có bài KSĐN</v>
-      </c>
-      <c r="K75" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76">
-        <v>71</v>
-      </c>
-      <c r="B76" t="str">
-        <v>CS5</v>
-      </c>
-      <c r="C76" t="str">
-        <v>0501030605</v>
-      </c>
-      <c r="D76" t="str">
-        <v>Nguyễn Minh Anh</v>
-      </c>
-      <c r="E76" t="str">
-        <v>6.5_CS5</v>
-      </c>
-      <c r="F76" t="str">
-        <v>Khối 6</v>
-      </c>
-      <c r="G76" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H76" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I76" t="str">
-        <v>Toán: 4; Tiếng Việt: 9; Ngữ Văn: 9; Tiếng Anh: 3.0 (Tổng: 30)</v>
-      </c>
-      <c r="J76" t="str">
-        <v>Toán: 6.75; Tiếng Việt: 10; Ngữ Văn: 8.25; Tiếng Anh: 8.7</v>
-      </c>
-      <c r="K76" t="str">
-        <v>Bứt phá ngoạn mục (+5.7)</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77">
-        <v>72</v>
-      </c>
-      <c r="B77" t="str">
-        <v>CS5</v>
-      </c>
-      <c r="C77" t="str">
-        <v>0601051037</v>
-      </c>
-      <c r="D77" t="str">
-        <v>Đỗ Duy Khôi</v>
-      </c>
-      <c r="E77" t="str">
-        <v>6.5_CS5</v>
-      </c>
-      <c r="F77" t="str">
-        <v>Khối 6</v>
-      </c>
-      <c r="G77" t="str">
-        <v>Tiếng Anh, Toán</v>
-      </c>
-      <c r="H77" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I77" t="str">
-        <v>Toán: 4; Tiếng Việt: 7; Ngữ Văn: 3; Tiếng Anh: 5.5 (Tổng: 55)</v>
-      </c>
-      <c r="J77" t="str">
-        <v>Toán: 2.25; Ngữ Văn: 6.75; Tiếng Anh: 4.5</v>
-      </c>
-      <c r="K77" t="str">
-        <v>Dưới TB môn Anh (4.5), cần phụ đạo</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78">
-        <v>73</v>
-      </c>
-      <c r="B78" t="str">
-        <v>CS5</v>
-      </c>
-      <c r="C78" t="str">
-        <v>0601051152</v>
-      </c>
-      <c r="D78" t="str">
-        <v>Lê Nguyễn Hoàng Bảo</v>
-      </c>
-      <c r="E78" t="str">
-        <v>7.5_CS5</v>
-      </c>
-      <c r="F78" t="str">
-        <v>Khối 7</v>
-      </c>
-      <c r="G78" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H78" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I78" t="str">
-        <v>Ngữ Văn: 5; Tiếng Anh: 1.7 (Tổng: 16.7)</v>
-      </c>
-      <c r="J78" t="str">
-        <v>Toán: 8.5; Ngữ Văn: 7; Tiếng Anh: 3.2</v>
-      </c>
-      <c r="K78" t="str">
-        <v>Tiến bộ rõ rệt (+1.5)</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79">
-        <v>74</v>
-      </c>
-      <c r="B79" t="str">
-        <v>CS5</v>
-      </c>
-      <c r="C79" t="str">
-        <v>0701050069</v>
-      </c>
-      <c r="D79" t="str">
-        <v>Nguyễn Hoàng Đạt</v>
-      </c>
-      <c r="E79" t="str">
-        <v>3.2INT_CS5</v>
-      </c>
-      <c r="F79" t="str">
-        <v>Khối 3</v>
-      </c>
-      <c r="G79" t="str">
-        <v>Chung / Theo dõi</v>
-      </c>
-      <c r="H79" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I79" t="str">
-        <v>Toán: 2; Tiếng Việt: 1; Tiếng Anh: 6.6 (Tổng: 66)</v>
-      </c>
-      <c r="J79" t="str">
-        <v>Tiếng Việt: 2; Tiếng Anh: 7.8</v>
-      </c>
-      <c r="K79" t="str">
-        <v>Tiến bộ rõ rệt (+1.2)</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80">
-        <v>75</v>
-      </c>
-      <c r="B80" t="str">
-        <v>CS5</v>
-      </c>
-      <c r="C80" t="str">
-        <v>0701050068</v>
-      </c>
-      <c r="D80" t="str">
-        <v>Nguyễn Hoàng Phúc</v>
-      </c>
-      <c r="E80" t="str">
-        <v>5.2INT_CS5</v>
-      </c>
-      <c r="F80" t="str">
-        <v>Khối 5</v>
-      </c>
-      <c r="G80" t="str">
-        <v>Chung / Theo dõi</v>
-      </c>
-      <c r="H80" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I80" t="str">
-        <v>Toán: 1; Tiếng Việt: 1; Tiếng Anh: 7.2 (Tổng: 72)</v>
-      </c>
-      <c r="J80" t="str">
-        <v>Tiếng Việt: 1; Tiếng Anh: 9.2</v>
-      </c>
-      <c r="K80" t="str">
-        <v>Tiến bộ rõ rệt (+2)</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81">
-        <v>76</v>
-      </c>
-      <c r="B81" t="str">
-        <v>CS5</v>
-      </c>
-      <c r="C81" t="str">
-        <v>0701030411</v>
-      </c>
-      <c r="D81" t="str">
-        <v>Trần Minh Huy</v>
-      </c>
-      <c r="E81" t="str">
-        <v>2.6_CS5</v>
-      </c>
-      <c r="F81" t="str">
-        <v>Khối 2</v>
-      </c>
-      <c r="G81" t="str">
-        <v>Tiếng Anh</v>
-      </c>
-      <c r="H81" t="str">
-        <v>Đủ điểm</v>
-      </c>
-      <c r="I81" t="str">
-        <v>Tiếng Anh: 7.0 (Tổng: 70)</v>
-      </c>
-      <c r="J81" t="str">
-        <v>Toán: 10; Tiếng Việt: 9.5; Tiếng Anh: 7.4</v>
-      </c>
-      <c r="K81" t="str">
-        <v>Đạt chuẩn môn Anh (7.4)</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I134"/>
   </ignoredErrors>
 </worksheet>
 </file>